--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45645</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45833</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>46008</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 46384-2025</t>
+          <t>A 49789-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45925</v>
+        <v>45212</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1175,16 +1175,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1208,263 +1208,263 @@
         <v>2</v>
       </c>
       <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Klippfrullania
+Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 23796-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Vitplätt
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 46384-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U9" t="n">
         <v>2</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Duvhök
 Tjäder</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46384-2025 artfynd.xlsx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46384-2025 karta.png", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46384-2025 georefererad karta.tif", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46384-2025 FSC-klagomål.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46384-2025 FSC-klagomål mail.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46384-2025 tillsynsbegäran.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46384-2025 tillsynsbegäran mail.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46384-2025 prioriterade fågelarter.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 23796-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46164</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Vitplätt
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 49789-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45212</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Klippfrullania
-Trubbfjädermossa</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
         <v/>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
         <v>44831</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>44586</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>45677</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 34574-2025</t>
+          <t>A 44926-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45847</v>
+        <v>45918</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7.4</v>
+        <v>3.8</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1865,46 +1865,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 6042-2024</t>
+          <t>A 34574-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45336</v>
+        <v>45847</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,13 +1934,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>7.4</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1974,42 +1974,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 44926-2025</t>
+          <t>A 6042-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45918</v>
+        <v>45336</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2039,13 +2039,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2075,39 +2075,39 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
         <v>45933</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>45925</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>44462</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>44739</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45337</v>
+        <v>44564</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2853,7 +2853,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45371</v>
+        <v>45645</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>6.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2926,7 +2926,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44564</v>
+        <v>45734</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45734</v>
+        <v>45441</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3072,7 +3072,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45127</v>
+        <v>45567</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3145,7 +3145,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45880</v>
+        <v>45378</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44977</v>
+        <v>45127</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3291,7 +3291,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3308,7 +3308,7 @@
         <v>46078</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3369,7 +3369,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3386,7 +3386,7 @@
         <v>46078</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3464,7 +3464,7 @@
         <v>46078</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45644</v>
+        <v>45880</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45659</v>
+        <v>45072</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3671,7 +3671,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45645</v>
+        <v>45271</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45567</v>
+        <v>45782</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3817,7 +3817,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45441</v>
+        <v>46196</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3890,7 +3890,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45240</v>
+        <v>46244</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3977,10 +3977,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45782</v>
+        <v>45321</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4036,7 +4036,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4046,14 +4046,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45769</v>
+        <v>46239</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4109,7 +4109,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45378</v>
+        <v>44586</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4182,7 +4182,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45321</v>
+        <v>46261</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4269,10 +4269,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46196</v>
+        <v>45337</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4328,7 +4328,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45371</v>
+        <v>46230</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.7</v>
+        <v>7.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4401,7 +4401,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46244</v>
+        <v>45659</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4488,10 +4488,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44586</v>
+        <v>44977</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4547,7 +4547,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45084</v>
+        <v>45644</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4630,14 +4630,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46239</v>
+        <v>45371</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46261</v>
+        <v>45084</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4766,7 +4766,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45271</v>
+        <v>45240</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4839,7 +4839,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45072</v>
+        <v>45371</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4912,7 +4912,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46230</v>
+        <v>45769</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>7.6</v>
+        <v>2.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5002,7 +5002,7 @@
         <v>45737</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>46028</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45645</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45833</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>46008</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 49789-2023</t>
+          <t>A 23796-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45212</v>
+        <v>46164</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1175,16 +1175,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1211,150 +1211,150 @@
         <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Vitplätt
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 49789-2023</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45212</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Klippfrullania
 Trubbfjädermossa</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 23796-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46164</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Vitplätt
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
         <v/>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
         <v>45925</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>44831</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>44586</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2842-2025</t>
+          <t>A 44926-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45677</v>
+        <v>45918</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1753,53 +1753,49 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 44926-2025</t>
+          <t>A 48265-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1813,10 +1809,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45918</v>
+        <v>45933</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1829,7 +1825,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1862,49 +1858,53 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 34574-2025</t>
+          <t>A 46379-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1914,14 +1914,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45847</v>
+        <v>45925</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1974,42 +1974,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 6042-2024</t>
+          <t>A 2842-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2023,10 +2027,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45336</v>
+        <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2039,13 +2043,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2072,49 +2076,53 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 48265-2025</t>
+          <t>A 34574-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2128,10 +2136,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45933</v>
+        <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2144,7 +2152,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>7.4</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2177,53 +2185,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46379-2025</t>
+          <t>A 6042-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2233,14 +2237,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45925</v>
+        <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2253,13 +2257,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2293,39 +2297,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 51537-2021</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44462</v>
+        <v>45337</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.2</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2707,7 +2707,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 26650-2022</t>
+          <t>A 51537-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44739</v>
+        <v>44462</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>7.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2780,7 +2780,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44564</v>
+        <v>45371</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2853,7 +2853,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45645</v>
+        <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.6</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2926,7 +2926,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 26650-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45734</v>
+        <v>44739</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45441</v>
+        <v>45127</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3072,7 +3072,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45567</v>
+        <v>45880</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3162,7 +3162,7 @@
         <v>45378</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45127</v>
+        <v>45321</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3308,7 +3308,7 @@
         <v>46078</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3369,7 +3369,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3386,7 +3386,7 @@
         <v>46078</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3464,7 +3464,7 @@
         <v>46078</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45880</v>
+        <v>45734</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45072</v>
+        <v>45371</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3671,7 +3671,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45271</v>
+        <v>44586</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45782</v>
+        <v>44977</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3817,7 +3817,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46196</v>
+        <v>45084</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3890,7 +3890,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46244</v>
+        <v>45644</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3977,10 +3977,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45321</v>
+        <v>45659</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4036,7 +4036,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4046,14 +4046,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46239</v>
+        <v>45645</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>6.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4109,7 +4109,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44586</v>
+        <v>45782</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4182,7 +4182,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46261</v>
+        <v>46196</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4269,10 +4269,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45337</v>
+        <v>46244</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4328,7 +4328,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46230</v>
+        <v>45567</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>7.6</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4401,7 +4401,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45659</v>
+        <v>45441</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4484,14 +4484,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44977</v>
+        <v>46239</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4547,7 +4547,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45644</v>
+        <v>45271</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45371</v>
+        <v>45240</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45084</v>
+        <v>46261</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4766,7 +4766,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45240</v>
+        <v>45769</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4839,7 +4839,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45371</v>
+        <v>45072</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4912,7 +4912,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45769</v>
+        <v>46230</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.8</v>
+        <v>7.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5002,7 +5002,7 @@
         <v>45737</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>46028</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE55"/>
+  <dimension ref="A1:AE56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45645</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45833</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 62768-2025</t>
+          <t>A 49789-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46008</v>
+        <v>45212</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1098,263 +1098,263 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Klippfrullania
+Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 62768-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
         <v>4</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>4</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Tjäder</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 62768-2025 artfynd.xlsx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 62768-2025 karta.png", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 62768-2025 georefererad karta.tif", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 62768-2025 FSC-klagomål.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 62768-2025 FSC-klagomål mail.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 62768-2025 tillsynsbegäran.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 62768-2025 tillsynsbegäran mail.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 62768-2025 prioriterade fågelarter.docx", "A 62768-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>A 23796-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D8" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+      <c r="E8" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>3.6</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>2</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>2</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>1</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Vitplätt
 Tjäder</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 49789-2023</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45212</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Klippfrullania
-Trubbfjädermossa</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
         <v/>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
         <v>45925</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>44831</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>44586</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 44926-2025</t>
+          <t>A 2842-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45918</v>
+        <v>45677</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1753,49 +1753,53 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 48265-2025</t>
+          <t>A 44926-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1809,10 +1813,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45933</v>
+        <v>45918</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1825,7 +1829,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1858,53 +1862,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 46379-2025</t>
+          <t>A 34574-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1914,14 +1914,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45925</v>
+        <v>45847</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1974,46 +1974,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2842-2025</t>
+          <t>A 6042-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2027,10 +2023,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45677</v>
+        <v>45336</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2043,13 +2039,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2076,53 +2072,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 34574-2025</t>
+          <t>A 48265-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2136,10 +2128,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45847</v>
+        <v>45933</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2152,7 +2144,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.4</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2185,49 +2177,53 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6042-2024</t>
+          <t>A 46379-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2237,14 +2233,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45336</v>
+        <v>45925</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2257,13 +2253,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2297,35 +2293,39 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
         <v/>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 51537-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45337</v>
+        <v>44462</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>7.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2707,7 +2707,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 51537-2021</t>
+          <t>A 26650-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44462</v>
+        <v>44739</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>7.2</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2780,7 +2780,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45371</v>
+        <v>44564</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2853,7 +2853,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44564</v>
+        <v>45734</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2926,7 +2926,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 26650-2022</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44739</v>
+        <v>45441</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45127</v>
+        <v>45567</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3072,7 +3072,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45880</v>
+        <v>45378</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45378</v>
+        <v>45127</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45321</v>
+        <v>45880</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3308,7 +3308,7 @@
         <v>46078</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3369,7 +3369,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3386,7 +3386,7 @@
         <v>46078</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3464,7 +3464,7 @@
         <v>46078</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45734</v>
+        <v>45645</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.1</v>
+        <v>6.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45371</v>
+        <v>45072</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3671,7 +3671,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44586</v>
+        <v>45271</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44977</v>
+        <v>45321</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3817,7 +3817,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45084</v>
+        <v>44586</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3890,7 +3890,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45644</v>
+        <v>45337</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3980,7 +3980,7 @@
         <v>45659</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4050,10 +4050,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45645</v>
+        <v>44977</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6.6</v>
+        <v>3.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4126,7 +4126,7 @@
         <v>45782</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46196</v>
+        <v>45644</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4269,10 +4269,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46244</v>
+        <v>46196</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4328,7 +4328,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45567</v>
+        <v>46244</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4401,7 +4401,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45441</v>
+        <v>45371</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4491,7 +4491,7 @@
         <v>46239</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45271</v>
+        <v>45084</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45240</v>
+        <v>46261</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46261</v>
+        <v>45240</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4766,7 +4766,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45769</v>
+        <v>46230</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.8</v>
+        <v>7.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4839,7 +4839,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45072</v>
+        <v>45371</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4912,7 +4912,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46230</v>
+        <v>45769</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>7.6</v>
+        <v>2.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4985,148 +4985,221 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
+          <t>A 38274-2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="E54" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>S 921-2025</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D54" s="1" t="n">
+      <c r="D55" s="1" t="n">
         <v>45737</v>
       </c>
-      <c r="E54" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
+      <c r="E55" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
         <v>0.3</v>
       </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>S 14-2026</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D55" s="1" t="n">
+      <c r="D56" s="1" t="n">
         <v>46028</v>
       </c>
-      <c r="E55" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" s="2" t="inlineStr"/>
+      <c r="E56" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45645</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45833</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 49789-2023</t>
+          <t>A 62768-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45212</v>
+        <v>46008</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1098,373 +1098,373 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 62768-2025 artfynd.xlsx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 62768-2025 karta.png", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 62768-2025 georefererad karta.tif", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 62768-2025 FSC-klagomål.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 62768-2025 FSC-klagomål mail.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 62768-2025 tillsynsbegäran.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 62768-2025 tillsynsbegäran mail.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 62768-2025 prioriterade fågelarter.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 23796-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>2</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Vitplätt
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 46384-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Duvhök
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46384-2025 artfynd.xlsx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46384-2025 karta.png", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46384-2025 georefererad karta.tif", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46384-2025 FSC-klagomål.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46384-2025 FSC-klagomål mail.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46384-2025 tillsynsbegäran.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46384-2025 tillsynsbegäran mail.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46384-2025 prioriterade fågelarter.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 49789-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45212</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Klippfrullania
 Trubbfjädermossa</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 62768-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46008</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>4</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 62768-2025 artfynd.xlsx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 62768-2025 karta.png", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 62768-2025 georefererad karta.tif", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 62768-2025 FSC-klagomål.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 62768-2025 FSC-klagomål mail.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 62768-2025 tillsynsbegäran.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 62768-2025 tillsynsbegäran mail.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 62768-2025 prioriterade fågelarter.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 23796-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46164</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Vitplätt
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 46384-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45925</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Duvhök
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46384-2025 artfynd.xlsx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46384-2025 karta.png", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46384-2025 georefererad karta.tif", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46384-2025 FSC-klagomål.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46384-2025 FSC-klagomål mail.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46384-2025 tillsynsbegäran.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46384-2025 tillsynsbegäran mail.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46384-2025 prioriterade fågelarter.docx", "A 46384-2025")</f>
         <v/>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
         <v>44831</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>44586</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>45677</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 44926-2025</t>
+          <t>A 34574-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45918</v>
+        <v>45847</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.8</v>
+        <v>7.4</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1865,46 +1865,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 34574-2025</t>
+          <t>A 6042-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45847</v>
+        <v>45336</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,13 +1934,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>7.4</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1974,42 +1974,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 6042-2024</t>
+          <t>A 44926-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45336</v>
+        <v>45918</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2039,13 +2039,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2075,39 +2075,39 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
         <v>45933</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>45925</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>44462</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>44739</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44564</v>
+        <v>45337</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2853,7 +2853,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45734</v>
+        <v>45371</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2926,7 +2926,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45441</v>
+        <v>44564</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45567</v>
+        <v>46078</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3028,8 +3028,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3072,7 +3077,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3086,10 +3091,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45378</v>
+        <v>46078</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3101,8 +3106,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3145,7 +3155,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3159,10 +3169,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45127</v>
+        <v>46078</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3174,8 +3184,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3218,7 +3233,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3232,10 +3247,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45880</v>
+        <v>45734</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3248,7 +3263,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3291,7 +3306,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3305,10 +3320,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46078</v>
+        <v>44977</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3320,13 +3335,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3369,7 +3379,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3383,10 +3393,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46078</v>
+        <v>45127</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3398,13 +3408,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3447,7 +3452,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3461,10 +3466,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46078</v>
+        <v>45880</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3476,13 +3481,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3525,7 +3525,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45645</v>
+        <v>45644</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6.6</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45072</v>
+        <v>45659</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3671,7 +3671,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45271</v>
+        <v>45782</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45321</v>
+        <v>45567</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3817,7 +3817,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44586</v>
+        <v>45441</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3890,7 +3890,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45337</v>
+        <v>46196</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3977,10 +3977,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45659</v>
+        <v>46244</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4036,7 +4036,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4050,10 +4050,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44977</v>
+        <v>45240</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4109,7 +4109,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45782</v>
+        <v>45769</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4182,7 +4182,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45644</v>
+        <v>45378</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4269,10 +4269,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46196</v>
+        <v>45321</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4328,7 +4328,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46244</v>
+        <v>46261</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4401,7 +4401,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45371</v>
+        <v>45645</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>6.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4484,14 +4484,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46239</v>
+        <v>45371</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4547,7 +4547,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45084</v>
+        <v>46230</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>7.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46261</v>
+        <v>44586</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45240</v>
+        <v>45084</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4766,7 +4766,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46230</v>
+        <v>46281</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>7.6</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4839,7 +4839,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4849,14 +4849,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45371</v>
+        <v>46239</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4912,7 +4912,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45769</v>
+        <v>45271</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4985,7 +4985,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46281</v>
+        <v>45072</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>45737</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>46028</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45645</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45833</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 62768-2025</t>
+          <t>A 49789-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46008</v>
+        <v>45212</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1098,373 +1098,373 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Klippfrullania
+Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 62768-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
         <v>4</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>4</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Tjäder</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 62768-2025 artfynd.xlsx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 62768-2025 karta.png", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 62768-2025 georefererad karta.tif", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 62768-2025 FSC-klagomål.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 62768-2025 FSC-klagomål mail.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 62768-2025 tillsynsbegäran.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 62768-2025 tillsynsbegäran mail.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 62768-2025 prioriterade fågelarter.docx", "A 62768-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>A 23796-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D8" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+      <c r="E8" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>3.6</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>2</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>2</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>1</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Vitplätt
 Tjäder</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 46384-2025</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D9" s="1" t="n">
         <v>45925</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E9" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>3.1</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Duvhök
 Tjäder</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46384-2025 artfynd.xlsx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46384-2025 karta.png", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46384-2025 georefererad karta.tif", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46384-2025 FSC-klagomål.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46384-2025 FSC-klagomål mail.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46384-2025 tillsynsbegäran.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46384-2025 tillsynsbegäran mail.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46384-2025 prioriterade fågelarter.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 49789-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45212</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Klippfrullania
-Trubbfjädermossa</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
         <v/>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
         <v>44831</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>44586</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2842-2025</t>
+          <t>A 44926-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45677</v>
+        <v>45918</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1753,53 +1753,49 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 34574-2025</t>
+          <t>A 48265-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1813,10 +1809,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45847</v>
+        <v>45933</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1829,7 +1825,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7.4</v>
+        <v>2.1</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1862,49 +1858,53 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 6042-2024</t>
+          <t>A 46379-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1914,14 +1914,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45336</v>
+        <v>45925</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,13 +1934,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1974,42 +1974,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 44926-2025</t>
+          <t>A 2842-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2023,10 +2027,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45918</v>
+        <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2039,7 +2043,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2072,49 +2076,53 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 48265-2025</t>
+          <t>A 34574-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2128,10 +2136,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45933</v>
+        <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2144,7 +2152,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>7.4</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2177,53 +2185,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46379-2025</t>
+          <t>A 6042-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2233,14 +2237,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45925</v>
+        <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2253,13 +2257,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2293,39 +2297,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>44462</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>44739</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45337</v>
+        <v>44564</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2853,7 +2853,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45371</v>
+        <v>45441</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2926,7 +2926,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44564</v>
+        <v>45567</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46078</v>
+        <v>45378</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3028,13 +3028,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3077,7 +3072,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3091,10 +3086,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46078</v>
+        <v>45734</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3106,13 +3101,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3155,7 +3145,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3169,10 +3159,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46078</v>
+        <v>45072</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3184,13 +3174,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3233,7 +3218,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3247,10 +3232,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45734</v>
+        <v>45271</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3263,7 +3248,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3306,7 +3291,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3320,10 +3305,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44977</v>
+        <v>45321</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3336,7 +3321,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3379,7 +3364,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3393,10 +3378,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45127</v>
+        <v>44586</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3409,7 +3394,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3452,7 +3437,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3466,10 +3451,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45880</v>
+        <v>45337</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3482,7 +3467,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3525,7 +3510,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3539,10 +3524,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45644</v>
+        <v>45659</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3555,7 +3540,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3598,7 +3583,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3612,10 +3597,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45659</v>
+        <v>44977</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3628,7 +3613,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3671,7 +3656,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3685,10 +3670,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45782</v>
+        <v>45645</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3701,7 +3686,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.9</v>
+        <v>6.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3744,7 +3729,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3758,10 +3743,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45567</v>
+        <v>45782</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3774,7 +3759,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3817,7 +3802,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3831,10 +3816,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45441</v>
+        <v>45644</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3847,7 +3832,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3890,7 +3875,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3904,10 +3889,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46196</v>
+        <v>46078</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3919,8 +3904,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3963,7 +3953,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3977,10 +3967,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46244</v>
+        <v>46078</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3992,8 +3982,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4036,7 +4031,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4050,10 +4045,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45240</v>
+        <v>46078</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4065,8 +4060,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4109,7 +4109,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45769</v>
+        <v>46196</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4182,7 +4182,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45378</v>
+        <v>46244</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4269,10 +4269,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45321</v>
+        <v>45371</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4328,7 +4328,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46261</v>
+        <v>45084</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4401,7 +4401,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45645</v>
+        <v>45240</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6.6</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4488,10 +4488,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45371</v>
+        <v>46261</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4547,7 +4547,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46230</v>
+        <v>45371</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>7.6</v>
+        <v>2.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44586</v>
+        <v>45769</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45084</v>
+        <v>46230</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>7.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4783,7 +4783,7 @@
         <v>46281</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>46239</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45271</v>
+        <v>45127</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4985,7 +4985,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45072</v>
+        <v>45880</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>45737</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>46028</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45645</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45833</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>45212</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>46164</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>45925</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>44831</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>44586</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>45918</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>45933</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45925</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>44462</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>44739</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>44564</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>45441</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>45567</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>45378</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45734</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>45072</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>45271</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>45321</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>44586</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>45337</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>45659</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>44977</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>45645</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>45782</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>45644</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>46078</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>46078</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>46078</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>46196</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>46244</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>45371</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>45084</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>45240</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>46261</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>45371</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>45769</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>46230</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>46281</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>46239</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>45127</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>45880</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>45737</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>46028</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45645</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45833</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>6.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
@@ -743,7 +743,7 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -755,28 +755,30 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
+        <v>2</v>
+      </c>
+      <c r="R3" t="n">
         <v>1</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav
+          <t>Gräddporing
+Vedskivlav
 Rävticka
 Trädporella
 Järpe
 Spillkråka
-Revlummer</t>
+Revlummer
+Äkta lopplummer</t>
         </is>
       </c>
       <c r="W3">
@@ -832,7 +834,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +943,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1052,7 +1054,7 @@
         <v>45212</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1158,7 +1160,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1270,7 @@
         <v>46164</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1378,7 +1380,7 @@
         <v>45925</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1488,7 +1490,7 @@
         <v>44831</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1600,7 @@
         <v>44586</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1690,7 +1692,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 44926-2025</t>
+          <t>A 6042-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1704,10 +1706,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45918</v>
+        <v>45336</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1720,13 +1722,13 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1756,46 +1758,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 48265-2025</t>
+          <t>A 44926-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1809,10 +1811,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45933</v>
+        <v>45918</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1825,7 +1827,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1858,53 +1860,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 46379-2025</t>
+          <t>A 48265-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1914,14 +1912,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45925</v>
+        <v>45933</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1932,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1967,53 +1965,53 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2842-2025</t>
+          <t>A 46379-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2023,14 +2021,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45677</v>
+        <v>45925</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2043,7 +2041,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2076,53 +2074,53 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 34574-2025</t>
+          <t>A 2842-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2136,10 +2134,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45847</v>
+        <v>45677</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2152,7 +2150,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.4</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2185,49 +2183,53 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6042-2024</t>
+          <t>A 34574-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2241,10 +2243,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45336</v>
+        <v>45847</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2257,13 +2259,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>7.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2297,35 +2299,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
     </row>
@@ -2349,7 +2351,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2427,7 +2429,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2505,7 +2507,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2578,7 +2580,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2651,7 +2653,7 @@
         <v>44462</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2724,7 +2726,7 @@
         <v>44739</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2797,7 +2799,7 @@
         <v>44564</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2870,7 +2872,7 @@
         <v>45441</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2943,7 +2945,7 @@
         <v>45567</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3016,7 +3018,7 @@
         <v>45378</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3072,7 +3074,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3086,10 +3088,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45734</v>
+        <v>45880</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3102,7 +3104,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3145,7 +3147,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3159,10 +3161,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45072</v>
+        <v>45734</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3175,7 +3177,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3218,7 +3220,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3232,10 +3234,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45271</v>
+        <v>45072</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3248,7 +3250,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3291,7 +3293,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3305,10 +3307,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45321</v>
+        <v>45271</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3321,7 +3323,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3364,7 +3366,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3378,10 +3380,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44586</v>
+        <v>45782</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3394,7 +3396,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3437,7 +3439,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3451,10 +3453,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45337</v>
+        <v>45321</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3467,7 +3469,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3510,7 +3512,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3524,10 +3526,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45659</v>
+        <v>44586</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3540,7 +3542,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3583,7 +3585,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3597,10 +3599,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44977</v>
+        <v>45337</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3613,7 +3615,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3673,7 +3675,7 @@
         <v>45645</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3729,7 +3731,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3743,10 +3745,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45782</v>
+        <v>45659</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3759,7 +3761,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3802,7 +3804,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3816,10 +3818,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45644</v>
+        <v>46196</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3832,7 +3834,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3875,7 +3877,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3889,10 +3891,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46078</v>
+        <v>44977</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3904,13 +3906,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3953,7 +3950,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3970,7 +3967,7 @@
         <v>46078</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3988,7 +3985,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4031,7 +4028,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4048,7 +4045,7 @@
         <v>46078</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4066,7 +4063,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4109,7 +4106,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4123,10 +4120,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46196</v>
+        <v>46078</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4138,8 +4135,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4182,7 +4184,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4196,10 +4198,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46244</v>
+        <v>45644</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4212,7 +4214,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4255,7 +4257,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4269,10 +4271,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45371</v>
+        <v>46261</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4285,7 +4287,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4328,7 +4330,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4342,10 +4344,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45084</v>
+        <v>45371</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4358,7 +4360,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4401,7 +4403,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4415,10 +4417,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45240</v>
+        <v>46230</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4431,7 +4433,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>7.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4474,7 +4476,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4488,10 +4490,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46261</v>
+        <v>45084</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4504,7 +4506,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4547,7 +4549,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4561,10 +4563,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45371</v>
+        <v>46281</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4577,7 +4579,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4620,7 +4622,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4630,14 +4632,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45769</v>
+        <v>46239</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4650,7 +4652,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4693,7 +4695,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4707,10 +4709,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46230</v>
+        <v>45240</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4723,7 +4725,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>7.6</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4766,7 +4768,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4780,10 +4782,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46281</v>
+        <v>46244</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4796,7 +4798,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4839,7 +4841,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4849,14 +4851,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46239</v>
+        <v>45371</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4869,7 +4871,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4912,7 +4914,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4926,10 +4928,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45127</v>
+        <v>45769</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4942,7 +4944,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4985,7 +4987,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4999,10 +5001,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45880</v>
+        <v>45127</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5075,7 +5077,7 @@
         <v>45737</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5148,7 +5150,7 @@
         <v>46028</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE56"/>
+  <dimension ref="A1:AE55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45645</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45833</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
@@ -755,23 +755,24 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Gräddporing
+Motaggsvamp
 Vedskivlav
 Rävticka
 Trädporella
@@ -834,7 +835,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +944,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1037,7 +1038,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 49789-2023</t>
+          <t>A 62768-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1051,10 +1052,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45212</v>
+        <v>46008</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1067,13 +1068,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1100,153 +1101,153 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 62768-2025 artfynd.xlsx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 62768-2025 karta.png", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 62768-2025 georefererad karta.tif", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 62768-2025 FSC-klagomål.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 62768-2025 FSC-klagomål mail.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 62768-2025 tillsynsbegäran.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 62768-2025 tillsynsbegäran mail.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 62768-2025 prioriterade fågelarter.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 49789-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45212</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Klippfrullania
 Trubbfjädermossa</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 62768-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46008</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>4</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 62768-2025 artfynd.xlsx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 62768-2025 karta.png", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 62768-2025 georefererad karta.tif", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 62768-2025 FSC-klagomål.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 62768-2025 FSC-klagomål mail.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 62768-2025 tillsynsbegäran.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 62768-2025 tillsynsbegäran mail.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 62768-2025 prioriterade fågelarter.docx", "A 62768-2025")</f>
         <v/>
       </c>
     </row>
@@ -1270,7 +1271,7 @@
         <v>46164</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1380,7 +1381,7 @@
         <v>45925</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1490,7 +1491,7 @@
         <v>44831</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1600,7 +1601,7 @@
         <v>44586</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1692,7 +1693,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 6042-2024</t>
+          <t>A 44926-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1706,10 +1707,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45336</v>
+        <v>45918</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1722,13 +1723,13 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1758,46 +1759,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 44926-2025</t>
+          <t>A 2842-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1811,10 +1812,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45918</v>
+        <v>45677</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1827,7 +1828,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1860,49 +1861,53 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 48265-2025</t>
+          <t>A 46379-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1912,14 +1917,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45933</v>
+        <v>45925</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1932,7 +1937,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1965,53 +1970,53 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 46379-2025</t>
+          <t>A 34574-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2021,14 +2026,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45925</v>
+        <v>45847</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2041,7 +2046,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2081,46 +2086,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 2842-2025</t>
+          <t>A 6042-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2134,10 +2135,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45677</v>
+        <v>45336</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2150,13 +2151,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2183,53 +2184,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 34574-2025</t>
+          <t>A 48265-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2243,10 +2240,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45847</v>
+        <v>45933</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2259,7 +2256,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>7.4</v>
+        <v>2.1</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2292,42 +2289,46 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
         <v/>
       </c>
     </row>
@@ -2351,7 +2352,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2429,7 +2430,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2507,7 +2508,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2580,7 +2581,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2636,7 +2637,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 51537-2021</t>
+          <t>A 26650-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2650,10 +2651,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44462</v>
+        <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2666,7 +2667,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.2</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2709,7 +2710,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 26650-2022</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2723,10 +2724,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44739</v>
+        <v>45659</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2739,7 +2740,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2782,7 +2783,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2796,10 +2797,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44564</v>
+        <v>45337</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2812,7 +2813,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2855,7 +2856,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2869,10 +2870,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45441</v>
+        <v>45371</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2885,7 +2886,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2928,7 +2929,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2942,10 +2943,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45567</v>
+        <v>44564</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2958,7 +2959,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3001,7 +3002,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3015,10 +3016,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45378</v>
+        <v>45734</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3031,7 +3032,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3074,7 +3075,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3088,10 +3089,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45880</v>
+        <v>45567</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3104,7 +3105,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3147,7 +3148,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3161,10 +3162,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45734</v>
+        <v>45441</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3177,7 +3178,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3220,7 +3221,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3234,10 +3235,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45072</v>
+        <v>45240</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3250,7 +3251,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3293,7 +3294,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3307,10 +3308,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45271</v>
+        <v>44977</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3323,7 +3324,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3366,7 +3367,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3380,10 +3381,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45782</v>
+        <v>45769</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3396,7 +3397,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3439,7 +3440,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3453,10 +3454,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45321</v>
+        <v>45644</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3469,7 +3470,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3512,7 +3513,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3526,10 +3527,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44586</v>
+        <v>45378</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3542,7 +3543,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3585,7 +3586,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3599,10 +3600,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45337</v>
+        <v>45321</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3615,7 +3616,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3675,7 +3676,7 @@
         <v>45645</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3731,7 +3732,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3745,10 +3746,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45659</v>
+        <v>45371</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3761,7 +3762,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3804,7 +3805,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3818,10 +3819,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46196</v>
+        <v>44586</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3834,7 +3835,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3877,7 +3878,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3891,10 +3892,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44977</v>
+        <v>46078</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3906,8 +3907,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3967,7 +3973,7 @@
         <v>46078</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4028,7 +4034,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4045,7 +4051,7 @@
         <v>46078</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4063,7 +4069,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4106,7 +4112,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4120,10 +4126,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46078</v>
+        <v>46244</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4135,13 +4141,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4184,7 +4185,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4198,10 +4199,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45644</v>
+        <v>45084</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4214,7 +4215,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4257,7 +4258,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4271,10 +4272,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46261</v>
+        <v>45127</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4287,7 +4288,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4330,7 +4331,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4344,10 +4345,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45371</v>
+        <v>45880</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4360,7 +4361,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4403,7 +4404,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4417,10 +4418,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46230</v>
+        <v>45271</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4433,7 +4434,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>7.6</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4476,7 +4477,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4490,10 +4491,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45084</v>
+        <v>45072</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4506,7 +4507,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4549,7 +4550,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4563,10 +4564,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46281</v>
+        <v>45782</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4579,7 +4580,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4622,7 +4623,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4632,14 +4633,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46239</v>
+        <v>46196</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4652,7 +4653,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4695,7 +4696,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4709,10 +4710,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45240</v>
+        <v>46261</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4725,7 +4726,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4768,7 +4769,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4782,10 +4783,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46244</v>
+        <v>46230</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4798,7 +4799,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>7.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4841,7 +4842,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4855,10 +4856,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45371</v>
+        <v>46281</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4871,7 +4872,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4914,7 +4915,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4924,14 +4925,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45769</v>
+        <v>46239</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4944,7 +4945,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4987,24 +4988,24 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>S 921-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45127</v>
+        <v>45737</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5017,7 +5018,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5057,10 +5058,10 @@
       </c>
       <c r="V54" s="2" t="inlineStr"/>
     </row>
-    <row r="55" ht="15" customHeight="1">
+    <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S 921-2025</t>
+          <t>S 14-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5074,10 +5075,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45737</v>
+        <v>46028</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5090,7 +5091,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5129,79 +5130,6 @@
         <v>0</v>
       </c>
       <c r="V55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>S 14-2026</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="n">
-        <v>46028</v>
-      </c>
-      <c r="E56" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45645</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45833</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 62768-2025</t>
+          <t>A 49789-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46008</v>
+        <v>45212</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1101,153 +1101,153 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Klippfrullania
+Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 62768-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
         <v>4</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>4</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Tjäder</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 62768-2025 artfynd.xlsx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 62768-2025 karta.png", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 62768-2025 georefererad karta.tif", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 62768-2025 FSC-klagomål.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 62768-2025 FSC-klagomål mail.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 62768-2025 tillsynsbegäran.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 62768-2025 tillsynsbegäran mail.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 62768-2025 prioriterade fågelarter.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 49789-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45212</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Klippfrullania
-Trubbfjädermossa</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
         <v/>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
         <v>46164</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>45925</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>44831</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>44586</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 44926-2025</t>
+          <t>A 6042-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1707,10 +1707,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45918</v>
+        <v>45336</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1759,46 +1759,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 2842-2025</t>
+          <t>A 44926-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45677</v>
+        <v>45918</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1861,53 +1861,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 46379-2025</t>
+          <t>A 48265-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1917,14 +1913,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45925</v>
+        <v>45933</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1937,7 +1933,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1970,53 +1966,53 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 34574-2025</t>
+          <t>A 46379-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2026,14 +2022,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45847</v>
+        <v>45925</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2046,7 +2042,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2086,42 +2082,46 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 6042-2024</t>
+          <t>A 2842-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2135,10 +2135,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45336</v>
+        <v>45677</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2151,13 +2151,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2184,49 +2184,53 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 48265-2025</t>
+          <t>A 34574-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2240,10 +2244,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45933</v>
+        <v>45847</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2256,7 +2260,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.1</v>
+        <v>7.4</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2289,46 +2293,42 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45659</v>
+        <v>44564</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45337</v>
+        <v>45441</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2856,7 +2856,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45371</v>
+        <v>45567</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2929,7 +2929,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44564</v>
+        <v>45378</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3002,7 +3002,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45734</v>
+        <v>45127</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3075,7 +3075,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3089,10 +3089,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45567</v>
+        <v>45734</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3162,10 +3162,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45441</v>
+        <v>45880</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3221,7 +3221,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45240</v>
+        <v>45072</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3294,7 +3294,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44977</v>
+        <v>45271</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3367,7 +3367,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45769</v>
+        <v>45321</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3440,7 +3440,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3454,10 +3454,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45644</v>
+        <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3527,10 +3527,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45378</v>
+        <v>45337</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3600,10 +3600,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45321</v>
+        <v>45645</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>6.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3659,7 +3659,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45645</v>
+        <v>45659</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6.6</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3732,7 +3732,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3746,10 +3746,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45371</v>
+        <v>44977</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3805,7 +3805,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44586</v>
+        <v>45782</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3895,7 +3895,7 @@
         <v>46078</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3956,7 +3956,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3973,7 +3973,7 @@
         <v>46078</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4051,7 +4051,7 @@
         <v>46078</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46244</v>
+        <v>45644</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4185,7 +4185,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45084</v>
+        <v>46196</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4258,7 +4258,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45127</v>
+        <v>45371</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4331,7 +4331,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45880</v>
+        <v>46261</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4404,7 +4404,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45271</v>
+        <v>45084</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4477,7 +4477,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45072</v>
+        <v>45240</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45782</v>
+        <v>46230</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.9</v>
+        <v>7.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4623,7 +4623,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46196</v>
+        <v>45371</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4696,7 +4696,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4710,10 +4710,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46261</v>
+        <v>45769</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4769,7 +4769,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46230</v>
+        <v>46281</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>7.6</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4842,7 +4842,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4852,14 +4852,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46281</v>
+        <v>46239</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4915,7 +4915,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4925,14 +4925,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>45737</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>46028</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45645</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45833</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 49789-2023</t>
+          <t>A 62768-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45212</v>
+        <v>46008</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1101,373 +1101,373 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 62768-2025 artfynd.xlsx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 62768-2025 karta.png", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 62768-2025 georefererad karta.tif", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 62768-2025 FSC-klagomål.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 62768-2025 FSC-klagomål mail.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 62768-2025 tillsynsbegäran.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 62768-2025 tillsynsbegäran mail.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 62768-2025 prioriterade fågelarter.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 23796-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>2</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Vitplätt
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 46384-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Duvhök
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46384-2025 artfynd.xlsx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46384-2025 karta.png", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46384-2025 georefererad karta.tif", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46384-2025 FSC-klagomål.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46384-2025 FSC-klagomål mail.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46384-2025 tillsynsbegäran.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46384-2025 tillsynsbegäran mail.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46384-2025 prioriterade fågelarter.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 49789-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45212</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Klippfrullania
 Trubbfjädermossa</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 62768-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46008</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>4</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 62768-2025 artfynd.xlsx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 62768-2025 karta.png", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 62768-2025 georefererad karta.tif", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 62768-2025 FSC-klagomål.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 62768-2025 FSC-klagomål mail.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 62768-2025 tillsynsbegäran.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 62768-2025 tillsynsbegäran mail.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 62768-2025 prioriterade fågelarter.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 23796-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46164</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Vitplätt
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 46384-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45925</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Duvhök
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46384-2025 artfynd.xlsx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46384-2025 karta.png", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46384-2025 georefererad karta.tif", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46384-2025 FSC-klagomål.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46384-2025 FSC-klagomål mail.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46384-2025 tillsynsbegäran.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46384-2025 tillsynsbegäran mail.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46384-2025 prioriterade fågelarter.docx", "A 46384-2025")</f>
         <v/>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
         <v>44831</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>44586</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 6042-2024</t>
+          <t>A 44926-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1707,10 +1707,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45336</v>
+        <v>45918</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1759,46 +1759,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 44926-2025</t>
+          <t>A 2842-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45918</v>
+        <v>45677</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1861,42 +1861,46 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
         <v/>
       </c>
     </row>
@@ -1920,7 +1924,7 @@
         <v>45933</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2012,7 +2016,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 46379-2025</t>
+          <t>A 34574-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2022,14 +2026,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45925</v>
+        <v>45847</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2042,7 +2046,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2082,46 +2086,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 2842-2025</t>
+          <t>A 6042-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2135,10 +2135,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45677</v>
+        <v>45336</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2151,13 +2151,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2184,53 +2184,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 34574-2025</t>
+          <t>A 46379-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2240,14 +2236,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45847</v>
+        <v>45925</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2260,7 +2256,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2300,35 +2296,39 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
         <v/>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44564</v>
+        <v>45337</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45441</v>
+        <v>45371</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2856,7 +2856,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45567</v>
+        <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2929,7 +2929,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45378</v>
+        <v>45645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>6.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3002,7 +3002,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45127</v>
+        <v>45734</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3075,7 +3075,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3089,10 +3089,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45734</v>
+        <v>46078</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3104,8 +3104,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3148,7 +3153,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3162,10 +3167,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45880</v>
+        <v>46078</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3177,8 +3182,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3221,7 +3231,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3235,10 +3245,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45072</v>
+        <v>46078</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3250,8 +3260,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3294,7 +3309,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3308,10 +3323,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45271</v>
+        <v>44977</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3324,7 +3339,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3367,7 +3382,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3381,10 +3396,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45321</v>
+        <v>45644</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3397,7 +3412,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3440,7 +3455,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3454,10 +3469,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44586</v>
+        <v>45659</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3470,7 +3485,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3513,7 +3528,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3527,10 +3542,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45337</v>
+        <v>45782</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3543,7 +3558,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3586,7 +3601,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3600,10 +3615,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45645</v>
+        <v>45127</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3616,7 +3631,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>6.6</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3659,7 +3674,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3673,10 +3688,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45659</v>
+        <v>46196</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3689,7 +3704,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3732,7 +3747,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3746,10 +3761,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44977</v>
+        <v>45880</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3762,7 +3777,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3805,7 +3820,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3819,10 +3834,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45782</v>
+        <v>45567</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3835,7 +3850,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3878,7 +3893,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3892,10 +3907,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46078</v>
+        <v>45441</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3907,13 +3922,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3956,7 +3966,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3970,10 +3980,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46078</v>
+        <v>45240</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3985,13 +3995,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4034,7 +4039,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4048,10 +4053,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46078</v>
+        <v>45769</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4063,13 +4068,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4112,7 +4112,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45644</v>
+        <v>46261</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4185,7 +4185,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46196</v>
+        <v>45378</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4258,7 +4258,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45371</v>
+        <v>45321</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4331,7 +4331,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46261</v>
+        <v>46230</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>7.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4404,7 +4404,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45084</v>
+        <v>46281</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4477,7 +4477,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4487,14 +4487,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45240</v>
+        <v>46239</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46230</v>
+        <v>45371</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>7.6</v>
+        <v>2.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4623,7 +4623,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45371</v>
+        <v>44586</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4696,7 +4696,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4710,10 +4710,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45769</v>
+        <v>46244</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4769,7 +4769,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46281</v>
+        <v>45084</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4842,7 +4842,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4852,14 +4852,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46239</v>
+        <v>45271</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4915,7 +4915,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46244</v>
+        <v>45072</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>45737</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>46028</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45645</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45833</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>46008</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46164</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>45925</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>45212</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>44831</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>44586</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45918</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>45677</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>45933</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>45847</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>45336</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>45925</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>45337</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>45371</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>45645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>45734</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>46078</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>46078</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>46078</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44977</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>45644</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>45659</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>45782</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>45127</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>46196</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>45880</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45567</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>45441</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>45240</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>45769</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>46261</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>45378</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>45321</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>46230</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>46281</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>46239</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>45371</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>44586</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>46244</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>45084</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>45271</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>45072</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>45737</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>46028</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 61167-2024</t>
+          <t>A 31321-2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45645</v>
+        <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="J2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -641,18 +641,136 @@
         <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
+        <v>10</v>
+      </c>
+      <c r="T2" t="n">
+        <v>14</v>
+      </c>
+      <c r="U2" t="n">
+        <v>14</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Gräddporing
+Motaggsvamp
+Vedskivlav
+Rävticka
+Trädporella
+Järpe
+Spillkråka
+Tjäder
+Revlummer
+Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 31321-2025 artfynd.xlsx", "A 31321-2025")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 31321-2025 karta.png", "A 31321-2025")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 31321-2025 georefererad karta.tif", "A 31321-2025")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 31321-2025 FSC-klagomål.docx", "A 31321-2025")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 31321-2025 FSC-klagomål mail.docx", "A 31321-2025")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 31321-2025 tillsynsbegäran.docx", "A 31321-2025")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 31321-2025 tillsynsbegäran mail.docx", "A 31321-2025")</f>
+        <v/>
+      </c>
+      <c r="AE2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 31321-2025 prioriterade fågelarter.docx", "A 31321-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 61167-2024</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45645</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" t="n">
         <v>9</v>
       </c>
-      <c r="T2" t="n">
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>9</v>
       </c>
-      <c r="U2" t="n">
+      <c r="T3" t="n">
         <v>9</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="U3" t="n">
+        <v>9</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Duvhök
 Järnsparv
@@ -665,153 +783,36 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 61167-2024 artfynd.xlsx", "A 61167-2024")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 61167-2024 karta.png", "A 61167-2024")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 61167-2024 georefererad karta.tif", "A 61167-2024")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 61167-2024 FSC-klagomål.docx", "A 61167-2024")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 61167-2024 FSC-klagomål mail.docx", "A 61167-2024")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 61167-2024 tillsynsbegäran.docx", "A 61167-2024")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 61167-2024 tillsynsbegäran mail.docx", "A 61167-2024")</f>
         <v/>
       </c>
-      <c r="AE2">
+      <c r="AE3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 61167-2024 prioriterade fågelarter.docx", "A 61167-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 31321-2025</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>45833</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>9</v>
-      </c>
-      <c r="T3" t="n">
-        <v>13</v>
-      </c>
-      <c r="U3" t="n">
-        <v>13</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Gräddporing
-Motaggsvamp
-Vedskivlav
-Rävticka
-Trädporella
-Järpe
-Spillkråka
-Revlummer
-Äkta lopplummer</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 31321-2025 artfynd.xlsx", "A 31321-2025")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 31321-2025 karta.png", "A 31321-2025")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 31321-2025 georefererad karta.tif", "A 31321-2025")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 31321-2025 FSC-klagomål.docx", "A 31321-2025")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 31321-2025 FSC-klagomål mail.docx", "A 31321-2025")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 31321-2025 tillsynsbegäran.docx", "A 31321-2025")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 31321-2025 tillsynsbegäran mail.docx", "A 31321-2025")</f>
-        <v/>
-      </c>
-      <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 31321-2025 prioriterade fågelarter.docx", "A 31321-2025")</f>
         <v/>
       </c>
     </row>
@@ -835,7 +836,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +945,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -960,7 +961,7 @@
         <v>5.1</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -987,19 +988,20 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
+        <v>5</v>
+      </c>
+      <c r="U5" t="n">
         <v>4</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Duvhök
 Vitplätt
-Spillkråka</t>
+Spillkråka
+Tjäder</t>
         </is>
       </c>
       <c r="W5">
@@ -1055,7 +1057,7 @@
         <v>46008</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1167,7 @@
         <v>46164</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1211,10 +1213,10 @@
         <v>2</v>
       </c>
       <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
         <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
@@ -1275,7 +1277,7 @@
         <v>45925</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1385,7 +1387,7 @@
         <v>45212</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1491,7 +1493,7 @@
         <v>44831</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1601,7 +1603,7 @@
         <v>44586</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1710,7 +1712,7 @@
         <v>45918</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1815,7 +1817,7 @@
         <v>45677</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1924,7 +1926,7 @@
         <v>45933</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2033,7 +2035,7 @@
         <v>45847</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2138,7 +2140,7 @@
         <v>45336</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2243,7 +2245,7 @@
         <v>45925</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2352,7 +2354,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2430,7 +2432,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2508,7 +2510,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2581,7 +2583,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2654,7 +2656,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2727,7 +2729,7 @@
         <v>45337</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2800,7 +2802,7 @@
         <v>45371</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2873,7 +2875,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2946,7 +2948,7 @@
         <v>45645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3019,7 +3021,7 @@
         <v>45734</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3092,7 +3094,7 @@
         <v>46078</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3170,7 +3172,7 @@
         <v>46078</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3248,7 +3250,7 @@
         <v>46078</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3326,7 +3328,7 @@
         <v>44977</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3399,7 +3401,7 @@
         <v>45644</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3472,7 +3474,7 @@
         <v>45659</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3545,7 +3547,7 @@
         <v>45782</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3618,7 +3620,7 @@
         <v>45127</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3691,7 +3693,7 @@
         <v>46196</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3764,7 +3766,7 @@
         <v>45880</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3837,7 +3839,7 @@
         <v>45567</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3910,7 +3912,7 @@
         <v>45441</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3983,7 +3985,7 @@
         <v>45240</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4056,7 +4058,7 @@
         <v>45769</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4129,7 +4131,7 @@
         <v>46261</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4202,7 +4204,7 @@
         <v>45378</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4275,7 +4277,7 @@
         <v>45321</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4348,7 +4350,7 @@
         <v>46230</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4421,7 +4423,7 @@
         <v>46281</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4494,7 +4496,7 @@
         <v>46239</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4567,7 +4569,7 @@
         <v>45371</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4640,7 +4642,7 @@
         <v>44586</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4713,7 +4715,7 @@
         <v>46244</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4786,7 +4788,7 @@
         <v>45084</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4859,7 +4861,7 @@
         <v>45271</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4932,7 +4934,7 @@
         <v>45072</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5005,7 +5007,7 @@
         <v>45737</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5078,7 +5080,7 @@
         <v>46028</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>46008</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 23796-2026</t>
+          <t>A 49789-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46164</v>
+        <v>45212</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1180,16 +1180,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1213,263 +1213,263 @@
         <v>2</v>
       </c>
       <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Klippfrullania
+Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 23796-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
         <v>3</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>2</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Vitplätt
 Tjäder</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 46384-2025</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D9" s="1" t="n">
         <v>45925</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E9" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>3.1</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Duvhök
 Tjäder</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46384-2025 artfynd.xlsx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46384-2025 karta.png", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46384-2025 georefererad karta.tif", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46384-2025 FSC-klagomål.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46384-2025 FSC-klagomål mail.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46384-2025 tillsynsbegäran.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46384-2025 tillsynsbegäran mail.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46384-2025 prioriterade fågelarter.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 49789-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45212</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Klippfrullania
-Trubbfjädermossa</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
         <v/>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
         <v>44831</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>44586</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>45918</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>45677</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 48265-2025</t>
+          <t>A 34574-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45933</v>
+        <v>45847</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.1</v>
+        <v>7.4</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1972,53 +1972,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 34574-2025</t>
+          <t>A 6042-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2032,10 +2028,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45847</v>
+        <v>45336</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2048,13 +2044,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2088,42 +2084,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 6042-2024</t>
+          <t>A 48265-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2137,10 +2133,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45336</v>
+        <v>45933</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2153,13 +2149,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2186,42 +2182,46 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
         <v/>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
         <v>45925</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45337</v>
+        <v>44564</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2785,7 +2785,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45371</v>
+        <v>45734</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44564</v>
+        <v>45645</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>6.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2931,7 +2931,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2945,10 +2945,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45645</v>
+        <v>45441</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3004,7 +3004,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3018,10 +3018,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45734</v>
+        <v>45567</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3077,7 +3077,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46078</v>
+        <v>45378</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3106,13 +3106,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3155,7 +3150,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3169,10 +3164,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46078</v>
+        <v>45127</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3184,13 +3179,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3233,7 +3223,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3247,10 +3237,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46078</v>
+        <v>45880</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3262,13 +3252,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3311,7 +3296,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3325,10 +3310,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44977</v>
+        <v>46078</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3340,8 +3325,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3384,7 +3374,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3398,10 +3388,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45644</v>
+        <v>46078</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3413,8 +3403,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3457,7 +3452,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3471,10 +3466,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45659</v>
+        <v>46078</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3486,8 +3481,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45782</v>
+        <v>45072</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45127</v>
+        <v>45271</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46196</v>
+        <v>45321</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45880</v>
+        <v>44586</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45567</v>
+        <v>45337</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45441</v>
+        <v>45659</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3968,7 +3968,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45240</v>
+        <v>44977</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4041,7 +4041,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45769</v>
+        <v>45782</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46261</v>
+        <v>45644</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4187,7 +4187,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4201,10 +4201,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45378</v>
+        <v>46196</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4260,7 +4260,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45321</v>
+        <v>45371</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46230</v>
+        <v>46261</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>7.6</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4406,7 +4406,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46281</v>
+        <v>45084</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4479,7 +4479,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4489,14 +4489,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46239</v>
+        <v>45240</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4552,7 +4552,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4566,10 +4566,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45371</v>
+        <v>46230</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.7</v>
+        <v>7.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4625,7 +4625,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44586</v>
+        <v>45371</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4698,7 +4698,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46244</v>
+        <v>45769</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4771,7 +4771,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4785,10 +4785,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45084</v>
+        <v>46281</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4844,7 +4844,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4854,14 +4854,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45271</v>
+        <v>46239</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4917,7 +4917,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45072</v>
+        <v>46244</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5007,7 +5007,7 @@
         <v>45737</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>46028</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>46008</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 49789-2023</t>
+          <t>A 23796-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45212</v>
+        <v>46164</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1180,16 +1180,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1213,263 +1213,263 @@
         <v>2</v>
       </c>
       <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
         <v>2</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
       <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Vitplätt
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 46384-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Duvhök
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46384-2025 artfynd.xlsx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46384-2025 karta.png", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46384-2025 georefererad karta.tif", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46384-2025 FSC-klagomål.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46384-2025 FSC-klagomål mail.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46384-2025 tillsynsbegäran.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46384-2025 tillsynsbegäran mail.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46384-2025 prioriterade fågelarter.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 49789-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45212</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Klippfrullania
 Trubbfjädermossa</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 23796-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46164</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Vitplätt
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 46384-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45925</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Duvhök
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46384-2025 artfynd.xlsx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46384-2025 karta.png", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46384-2025 georefererad karta.tif", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46384-2025 FSC-klagomål.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46384-2025 FSC-klagomål mail.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46384-2025 tillsynsbegäran.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46384-2025 tillsynsbegäran mail.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46384-2025 prioriterade fågelarter.docx", "A 46384-2025")</f>
         <v/>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
         <v>44831</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>44586</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>45918</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>45677</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>45847</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>45336</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>45933</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>45925</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44564</v>
+        <v>45337</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2785,7 +2785,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45734</v>
+        <v>45371</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45645</v>
+        <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.6</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2931,7 +2931,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2945,10 +2945,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45441</v>
+        <v>45645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.8</v>
+        <v>6.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3004,7 +3004,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3018,10 +3018,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45567</v>
+        <v>45734</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3077,7 +3077,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45378</v>
+        <v>45127</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45127</v>
+        <v>45880</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45880</v>
+        <v>44977</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3296,7 +3296,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46078</v>
+        <v>45644</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3325,13 +3325,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3391,7 +3386,7 @@
         <v>46078</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3452,7 +3447,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3469,7 +3464,7 @@
         <v>46078</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3487,7 +3482,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3530,7 +3525,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3544,10 +3539,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45072</v>
+        <v>46078</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3559,8 +3554,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45271</v>
+        <v>45659</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45321</v>
+        <v>45567</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44586</v>
+        <v>45441</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45337</v>
+        <v>45240</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45659</v>
+        <v>45782</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3968,7 +3968,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44977</v>
+        <v>45769</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4041,7 +4041,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45782</v>
+        <v>45378</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45644</v>
+        <v>45321</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4204,7 +4204,7 @@
         <v>46196</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4277,7 +4277,7 @@
         <v>45371</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46261</v>
+        <v>44586</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4423,7 +4423,7 @@
         <v>45084</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45240</v>
+        <v>46261</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4569,7 +4569,7 @@
         <v>46230</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45371</v>
+        <v>45271</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4698,7 +4698,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45769</v>
+        <v>46281</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4771,7 +4771,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4785,10 +4785,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46281</v>
+        <v>45072</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4861,7 +4861,7 @@
         <v>46239</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>46244</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>45737</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>46028</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         <v>6.4</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
         <v>2</v>
@@ -626,7 +626,7 @@
         <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -638,23 +638,24 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Gräddporing
+          <t>Blå kärrhök
+Gräddporing
 Motaggsvamp
 Vedskivlav
 Rävticka
@@ -719,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -762,13 +763,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -777,6 +778,7 @@
 Talltita
 Bergfink
 Spillkråka
+Timmerticka
 Tjäder
 Tofsmes
 Grönsiska
@@ -836,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -961,7 +963,7 @@
         <v>5.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -970,7 +972,7 @@
         <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -982,23 +984,24 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
+        <v>6</v>
+      </c>
+      <c r="U5" t="n">
         <v>5</v>
       </c>
-      <c r="U5" t="n">
-        <v>4</v>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Duvhök
+          <t>Blå kärrhök
+Duvhök
 Vitplätt
 Spillkråka
 Tjäder</t>
@@ -1040,7 +1043,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 62768-2025</t>
+          <t>A 49789-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1054,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46008</v>
+        <v>45212</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1070,13 +1073,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1103,490 +1106,490 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Klippfrullania
+Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 62768-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
         <v>4</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>4</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Tjäder</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 62768-2025 artfynd.xlsx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 62768-2025 karta.png", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 62768-2025 georefererad karta.tif", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 62768-2025 FSC-klagomål.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 62768-2025 FSC-klagomål mail.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 62768-2025 tillsynsbegäran.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 62768-2025 tillsynsbegäran mail.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 62768-2025 prioriterade fågelarter.docx", "A 62768-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 48265-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45933</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Timmerticka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 23796-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D9" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+      <c r="E9" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>3.6</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U9" t="n">
         <v>2</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Vitplätt
 Tjäder</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 46384-2025</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D10" s="1" t="n">
         <v>45925</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>3.1</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J10" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>2</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T10" t="n">
         <v>3</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U10" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Duvhök
 Tjäder</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46384-2025 artfynd.xlsx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46384-2025 karta.png", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46384-2025 georefererad karta.tif", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46384-2025 FSC-klagomål.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46384-2025 FSC-klagomål mail.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46384-2025 tillsynsbegäran.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46384-2025 tillsynsbegäran mail.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46384-2025 prioriterade fågelarter.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 49789-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45212</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Klippfrullania
-Trubbfjädermossa</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 42415-2022</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44831</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Hasselmus</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 42415-2022 artfynd.xlsx", "A 42415-2022")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 42415-2022 karta.png", "A 42415-2022")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 42415-2022 georefererad karta.tif", "A 42415-2022")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 42415-2022 FSC-klagomål.docx", "A 42415-2022")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 42415-2022 FSC-klagomål mail.docx", "A 42415-2022")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 42415-2022 tillsynsbegäran.docx", "A 42415-2022")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 42415-2022 tillsynsbegäran mail.docx", "A 42415-2022")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 3678-2022</t>
+          <t>A 46379-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1596,14 +1599,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44586</v>
+        <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1616,16 +1619,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1640,62 +1643,63 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Spillkråka
+Fiskgjuse</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 3678-2022 artfynd.xlsx", "A 3678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 3678-2022 karta.png", "A 3678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 3678-2022 georefererad karta.tif", "A 3678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 3678-2022 FSC-klagomål.docx", "A 3678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 3678-2022 FSC-klagomål mail.docx", "A 3678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 3678-2022 tillsynsbegäran.docx", "A 3678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 3678-2022 tillsynsbegäran mail.docx", "A 3678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
       <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 3678-2022 prioriterade fågelarter.docx", "A 3678-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 44926-2025</t>
+          <t>A 42415-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1709,10 +1713,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45918</v>
+        <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1724,8 +1728,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1761,46 +1770,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 42415-2022 artfynd.xlsx", "A 42415-2022")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 42415-2022 karta.png", "A 42415-2022")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 42415-2022 georefererad karta.tif", "A 42415-2022")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 42415-2022 FSC-klagomål.docx", "A 42415-2022")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 42415-2022 FSC-klagomål mail.docx", "A 42415-2022")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 42415-2022 tillsynsbegäran.docx", "A 42415-2022")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 42415-2022 tillsynsbegäran mail.docx", "A 42415-2022")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 2842-2025</t>
+          <t>A 3678-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1814,10 +1823,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45677</v>
+        <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1830,7 +1839,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1839,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1854,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1863,53 +1872,53 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 3678-2022 artfynd.xlsx", "A 3678-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 3678-2022 karta.png", "A 3678-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 3678-2022 georefererad karta.tif", "A 3678-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 3678-2022 FSC-klagomål.docx", "A 3678-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 3678-2022 FSC-klagomål mail.docx", "A 3678-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 3678-2022 tillsynsbegäran.docx", "A 3678-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 3678-2022 tillsynsbegäran mail.docx", "A 3678-2022")</f>
         <v/>
       </c>
       <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 3678-2022 prioriterade fågelarter.docx", "A 3678-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 34574-2025</t>
+          <t>A 2842-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1923,10 +1932,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45847</v>
+        <v>45677</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1939,7 +1948,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>7.4</v>
+        <v>2.7</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1972,49 +1981,53 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 6042-2024</t>
+          <t>A 34574-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2028,10 +2041,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45336</v>
+        <v>45847</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2044,13 +2057,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2084,42 +2097,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 48265-2025</t>
+          <t>A 6042-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2133,10 +2146,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45933</v>
+        <v>45336</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2149,13 +2162,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2182,53 +2195,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46379-2025</t>
+          <t>A 44926-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2238,14 +2247,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45925</v>
+        <v>45918</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2258,7 +2267,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2294,43 +2303,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
     </row>
@@ -2354,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2432,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2493,7 +2498,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 3673-2022</t>
+          <t>A 23877-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2507,10 +2512,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44586</v>
+        <v>44722</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2523,7 +2528,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2566,7 +2571,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 23877-2022</t>
+          <t>A 3673-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2580,10 +2585,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44722</v>
+        <v>44586</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2596,7 +2601,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2656,7 +2661,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2712,7 +2717,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2726,10 +2731,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45337</v>
+        <v>45659</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2785,7 +2790,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2799,10 +2804,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45371</v>
+        <v>45084</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2815,7 +2820,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2880,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2931,7 +2936,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2945,10 +2950,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45645</v>
+        <v>44977</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2961,7 +2966,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6.6</v>
+        <v>3.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3004,7 +3009,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3018,10 +3023,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45734</v>
+        <v>45240</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3034,7 +3039,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3077,7 +3082,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3091,10 +3096,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45127</v>
+        <v>45371</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3107,7 +3112,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3150,7 +3155,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3164,10 +3169,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45880</v>
+        <v>45769</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3180,7 +3185,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3223,7 +3228,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3237,10 +3242,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44977</v>
+        <v>45644</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3253,7 +3258,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3296,7 +3301,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3310,10 +3315,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45644</v>
+        <v>45072</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3326,7 +3331,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3369,7 +3374,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3383,10 +3388,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46078</v>
+        <v>45271</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3398,13 +3403,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46078</v>
+        <v>45371</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3476,13 +3476,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3525,7 +3520,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3539,10 +3534,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46078</v>
+        <v>45321</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3554,13 +3549,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3603,7 +3593,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3617,10 +3607,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45659</v>
+        <v>45441</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3633,7 +3623,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3676,7 +3666,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3690,10 +3680,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45567</v>
+        <v>44586</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3706,7 +3696,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3749,7 +3739,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3763,10 +3753,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45441</v>
+        <v>45337</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3779,7 +3769,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3822,7 +3812,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3836,10 +3826,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45240</v>
+        <v>45567</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3852,7 +3842,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3895,7 +3885,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3909,10 +3899,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45782</v>
+        <v>45378</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3925,7 +3915,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3968,7 +3958,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3982,10 +3972,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45769</v>
+        <v>45127</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3998,7 +3988,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4041,7 +4031,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4055,10 +4045,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45378</v>
+        <v>45734</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4071,7 +4061,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4114,7 +4104,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4128,10 +4118,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45321</v>
+        <v>45880</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4187,7 +4177,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4201,10 +4191,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46196</v>
+        <v>45645</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4217,7 +4207,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4260,7 +4250,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4274,10 +4264,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45371</v>
+        <v>46078</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4289,8 +4279,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4333,7 +4328,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4347,10 +4342,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44586</v>
+        <v>46078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4362,8 +4357,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4406,7 +4406,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45084</v>
+        <v>46078</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4435,8 +4435,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4479,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4493,10 +4498,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46261</v>
+        <v>45782</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4509,7 +4514,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4552,7 +4557,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4566,10 +4571,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46230</v>
+        <v>46196</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4582,7 +4587,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>7.6</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4625,7 +4630,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4639,10 +4644,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45271</v>
+        <v>46261</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4655,7 +4660,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4698,7 +4703,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4712,10 +4717,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46281</v>
+        <v>46230</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4728,7 +4733,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>7.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4771,7 +4776,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4785,10 +4790,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45072</v>
+        <v>46281</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4801,7 +4806,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4861,7 +4866,7 @@
         <v>46239</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4934,7 +4939,7 @@
         <v>46244</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5007,7 +5012,7 @@
         <v>45737</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5080,7 +5085,7 @@
         <v>46028</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 49789-2023</t>
+          <t>A 62768-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45212</v>
+        <v>46008</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,13 +1073,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1106,593 +1106,593 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 62768-2025 artfynd.xlsx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 62768-2025 karta.png", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 62768-2025 georefererad karta.tif", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 62768-2025 FSC-klagomål.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 62768-2025 FSC-klagomål mail.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 62768-2025 tillsynsbegäran.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 62768-2025 tillsynsbegäran mail.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 62768-2025 prioriterade fågelarter.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 46384-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J7" t="n">
         <v>2</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Duvhök
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46384-2025 artfynd.xlsx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46384-2025 karta.png", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46384-2025 georefererad karta.tif", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46384-2025 FSC-klagomål.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46384-2025 FSC-klagomål mail.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46384-2025 tillsynsbegäran.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46384-2025 tillsynsbegäran mail.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46384-2025 prioriterade fågelarter.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 23796-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Vitplätt
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 46379-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 48265-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45933</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Timmerticka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 49789-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45212</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Klippfrullania
 Trubbfjädermossa</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 62768-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46008</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>4</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 62768-2025 artfynd.xlsx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 62768-2025 karta.png", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 62768-2025 georefererad karta.tif", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 62768-2025 FSC-klagomål.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 62768-2025 FSC-klagomål mail.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 62768-2025 tillsynsbegäran.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 62768-2025 tillsynsbegäran mail.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 62768-2025 prioriterade fågelarter.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 48265-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45933</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Timmerticka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 23796-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46164</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Vitplätt
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 46384-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45925</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Duvhök
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46384-2025 artfynd.xlsx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46384-2025 karta.png", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46384-2025 georefererad karta.tif", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46384-2025 FSC-klagomål.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46384-2025 FSC-klagomål mail.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46384-2025 tillsynsbegäran.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46384-2025 tillsynsbegäran mail.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46384-2025 prioriterade fågelarter.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 46379-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45925</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Fiskgjuse</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
         <v/>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 2842-2025</t>
+          <t>A 44926-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45677</v>
+        <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1981,53 +1981,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 34574-2025</t>
+          <t>A 2842-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2041,10 +2037,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45847</v>
+        <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2057,7 +2053,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2090,49 +2086,53 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 6042-2024</t>
+          <t>A 34574-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45336</v>
+        <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2162,13 +2162,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>7.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2202,42 +2202,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 44926-2025</t>
+          <t>A 6042-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45918</v>
+        <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2303,39 +2303,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 23877-2022</t>
+          <t>A 3673-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44722</v>
+        <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2571,7 +2571,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3673-2022</t>
+          <t>A 23877-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44586</v>
+        <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2661,7 +2661,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45659</v>
+        <v>45337</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45084</v>
+        <v>45371</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2880,7 +2880,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44977</v>
+        <v>45645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3009,7 +3009,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45240</v>
+        <v>45734</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45371</v>
+        <v>46078</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3111,8 +3111,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3155,7 +3160,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3169,10 +3174,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45769</v>
+        <v>46078</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3184,8 +3189,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3228,7 +3238,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3242,10 +3252,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45644</v>
+        <v>46078</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3257,8 +3267,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3301,7 +3316,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3315,10 +3330,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45072</v>
+        <v>44977</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3331,7 +3346,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3374,7 +3389,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3388,10 +3403,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45271</v>
+        <v>45644</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3404,7 +3419,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3447,7 +3462,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3461,10 +3476,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45371</v>
+        <v>45659</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3477,7 +3492,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3520,7 +3535,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3534,10 +3549,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45321</v>
+        <v>45127</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3593,7 +3608,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3607,10 +3622,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45441</v>
+        <v>45880</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3623,7 +3638,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3666,7 +3681,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3680,10 +3695,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44586</v>
+        <v>45782</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3696,7 +3711,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3739,7 +3754,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3753,10 +3768,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45337</v>
+        <v>45567</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3769,7 +3784,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3812,7 +3827,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3826,10 +3841,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45567</v>
+        <v>45441</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3842,7 +3857,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3885,7 +3900,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3899,10 +3914,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45378</v>
+        <v>46196</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3915,7 +3930,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3958,7 +3973,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3972,10 +3987,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45127</v>
+        <v>45240</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3988,7 +4003,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4031,7 +4046,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4045,10 +4060,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45734</v>
+        <v>45769</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4061,7 +4076,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4104,7 +4119,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4118,10 +4133,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45880</v>
+        <v>45378</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4177,7 +4192,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4191,10 +4206,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45645</v>
+        <v>46261</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4207,7 +4222,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4250,7 +4265,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4264,10 +4279,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46078</v>
+        <v>45321</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4279,13 +4294,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4328,7 +4338,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4342,10 +4352,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46078</v>
+        <v>46230</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4357,13 +4367,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1.9</v>
+        <v>7.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4406,7 +4411,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4420,10 +4425,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46078</v>
+        <v>45371</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4435,13 +4440,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45782</v>
+        <v>44586</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46196</v>
+        <v>45084</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46261</v>
+        <v>46281</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4713,14 +4713,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46230</v>
+        <v>46239</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46281</v>
+        <v>46244</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4859,14 +4859,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46239</v>
+        <v>45271</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46244</v>
+        <v>45072</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>45737</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>46028</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46008</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 46384-2025</t>
+          <t>A 49789-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45925</v>
+        <v>45212</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1183,16 +1183,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1216,483 +1216,483 @@
         <v>2</v>
       </c>
       <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Klippfrullania
+Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 46384-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
         <v>3</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>2</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Duvhök
 Tjäder</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46384-2025 artfynd.xlsx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46384-2025 karta.png", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46384-2025 georefererad karta.tif", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46384-2025 FSC-klagomål.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46384-2025 FSC-klagomål mail.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46384-2025 tillsynsbegäran.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46384-2025 tillsynsbegäran mail.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46384-2025 prioriterade fågelarter.docx", "A 46384-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 48265-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45933</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Timmerticka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 46379-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 23796-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D11" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>3.6</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>2</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Vitplätt
 Tjäder</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 46379-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45925</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Fiskgjuse</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 48265-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45933</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Timmerticka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 49789-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45212</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Klippfrullania
-Trubbfjädermossa</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
         <v/>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45337</v>
+        <v>44564</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45371</v>
+        <v>45645</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>6.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44564</v>
+        <v>45734</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45645</v>
+        <v>45441</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3009,7 +3009,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45734</v>
+        <v>45567</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46078</v>
+        <v>45378</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3111,13 +3111,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3177,7 +3172,7 @@
         <v>46078</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3238,7 +3233,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3255,7 +3250,7 @@
         <v>46078</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3273,7 +3268,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3316,7 +3311,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3330,10 +3325,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44977</v>
+        <v>46078</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3345,8 +3340,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3389,7 +3389,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45644</v>
+        <v>45072</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45659</v>
+        <v>45127</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45127</v>
+        <v>45271</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45880</v>
+        <v>45321</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45782</v>
+        <v>44586</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45567</v>
+        <v>45337</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45441</v>
+        <v>45782</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46196</v>
+        <v>45880</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45240</v>
+        <v>45659</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45769</v>
+        <v>44977</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45378</v>
+        <v>46196</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4209,7 +4209,7 @@
         <v>46261</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45321</v>
+        <v>45644</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4355,7 +4355,7 @@
         <v>46230</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45371</v>
+        <v>46281</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4494,14 +4494,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44586</v>
+        <v>46239</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45084</v>
+        <v>46244</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46281</v>
+        <v>45371</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4713,14 +4713,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46239</v>
+        <v>45084</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46244</v>
+        <v>45240</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45271</v>
+        <v>45371</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45072</v>
+        <v>45769</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>45737</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>46028</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46008</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>45212</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45925</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>45933</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>45925</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>46164</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>44564</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>45645</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>45734</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>45441</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>45567</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45378</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>46078</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>46078</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>46078</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>45072</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>45127</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45271</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>45321</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>44586</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45337</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>45782</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45880</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>45659</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>44977</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>46196</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>46261</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>45644</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>46230</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>46281</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>46239</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>46244</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>45371</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>45084</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>45240</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>45371</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45769</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45737</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>46028</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46008</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>45212</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45925</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>45933</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>45925</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>46164</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>44564</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>45645</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>45734</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>45441</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>45567</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45378</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>46078</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>46078</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>46078</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>45072</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>45127</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45271</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>45321</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>44586</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45337</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>45782</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45880</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>45659</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>44977</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>46196</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>46261</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>45644</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>46230</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>46281</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>46239</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>46244</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>45371</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>45084</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>45240</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>45371</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45769</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45737</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>46028</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46008</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>45212</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45925</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 48265-2025</t>
+          <t>A 46379-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1379,14 +1379,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45933</v>
+        <v>45925</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1432,157 +1432,157 @@
         <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U9" t="n">
         <v>3</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
+          <t>Spillkråka
+Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 48265-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45933</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>Timmerticka
 Tjäder</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 46379-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45925</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Fiskgjuse</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
         <v/>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
         <v>46164</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 44926-2025</t>
+          <t>A 2842-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45918</v>
+        <v>45677</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1981,49 +1981,53 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2842-2025</t>
+          <t>A 34574-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2037,10 +2041,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45677</v>
+        <v>45847</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2053,7 +2057,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2086,53 +2090,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 34574-2025</t>
+          <t>A 44926-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45847</v>
+        <v>45918</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.4</v>
+        <v>3.8</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2198,39 +2198,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
         <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44564</v>
+        <v>45337</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45645</v>
+        <v>45371</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45734</v>
+        <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45441</v>
+        <v>45734</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3009,7 +3009,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45567</v>
+        <v>45127</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45378</v>
+        <v>45880</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46078</v>
+        <v>44977</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3184,13 +3184,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3233,7 +3228,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3247,10 +3242,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46078</v>
+        <v>45644</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3262,13 +3257,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3311,7 +3301,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3328,7 +3318,7 @@
         <v>46078</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3346,7 +3336,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3389,7 +3379,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3403,10 +3393,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45072</v>
+        <v>46078</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3418,8 +3408,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3462,7 +3457,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3476,10 +3471,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45127</v>
+        <v>46078</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3491,8 +3486,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45271</v>
+        <v>45659</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45321</v>
+        <v>45645</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>6.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44586</v>
+        <v>45567</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45337</v>
+        <v>45441</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>45782</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45880</v>
+        <v>45240</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45659</v>
+        <v>45769</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44977</v>
+        <v>46196</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46196</v>
+        <v>45378</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46261</v>
+        <v>45321</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45644</v>
+        <v>45371</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46230</v>
+        <v>44586</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>7.6</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46281</v>
+        <v>46261</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4494,14 +4494,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46239</v>
+        <v>45084</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46244</v>
+        <v>46230</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>7.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45371</v>
+        <v>46281</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4713,14 +4713,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45084</v>
+        <v>46239</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45240</v>
+        <v>45271</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45371</v>
+        <v>46244</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45769</v>
+        <v>45072</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>45737</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>46028</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE55"/>
+  <dimension ref="A1:AE56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 62768-2025</t>
+          <t>A 49789-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46008</v>
+        <v>45212</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,13 +1073,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1106,153 +1106,153 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Klippfrullania
+Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 62768-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
         <v>4</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>4</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Tjäder</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 62768-2025 artfynd.xlsx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 62768-2025 karta.png", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 62768-2025 georefererad karta.tif", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 62768-2025 FSC-klagomål.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 62768-2025 FSC-klagomål mail.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 62768-2025 tillsynsbegäran.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 62768-2025 tillsynsbegäran mail.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 62768-2025 prioriterade fågelarter.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 49789-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45212</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Klippfrullania
-Trubbfjädermossa</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
         <v/>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
         <v>45925</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 46379-2025</t>
+          <t>A 48265-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1379,14 +1379,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45925</v>
+        <v>45933</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1432,157 +1432,157 @@
         <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
         <v>3</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
+          <t>Timmerticka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 46379-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>Spillkråka
 Fiskgjuse</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 48265-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45933</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Timmerticka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
         <v/>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
         <v>46164</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 2842-2025</t>
+          <t>A 44926-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45677</v>
+        <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1981,53 +1981,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 34574-2025</t>
+          <t>A 2842-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2041,10 +2037,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45847</v>
+        <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2057,7 +2053,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2090,49 +2086,53 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 44926-2025</t>
+          <t>A 34574-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45918</v>
+        <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.8</v>
+        <v>7.4</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2198,39 +2198,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
         <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45337</v>
+        <v>44564</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45371</v>
+        <v>45441</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44564</v>
+        <v>45567</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2953,7 +2953,7 @@
         <v>45734</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45127</v>
+        <v>45378</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45880</v>
+        <v>46078</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3111,8 +3111,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3155,7 +3160,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3169,10 +3174,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44977</v>
+        <v>46078</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3184,8 +3189,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3228,7 +3238,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3242,10 +3252,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45644</v>
+        <v>46078</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3257,8 +3267,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3301,7 +3316,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3315,10 +3330,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46078</v>
+        <v>45127</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3330,13 +3345,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3379,7 +3389,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3393,10 +3403,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46078</v>
+        <v>45880</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3408,13 +3418,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3457,7 +3462,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3471,10 +3476,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46078</v>
+        <v>45645</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3486,13 +3491,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45659</v>
+        <v>45782</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45645</v>
+        <v>45072</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>6.6</v>
+        <v>1.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45567</v>
+        <v>46196</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45441</v>
+        <v>45271</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45782</v>
+        <v>45321</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45240</v>
+        <v>44586</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45769</v>
+        <v>45337</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46196</v>
+        <v>46261</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45378</v>
+        <v>45659</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45321</v>
+        <v>44977</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45371</v>
+        <v>46230</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.7</v>
+        <v>7.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44586</v>
+        <v>46281</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4421,14 +4421,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46261</v>
+        <v>46239</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45084</v>
+        <v>46244</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46230</v>
+        <v>45644</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>7.6</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46281</v>
+        <v>45371</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 41561-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4713,14 +4713,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46239</v>
+        <v>46301</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45271</v>
+        <v>45084</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46244</v>
+        <v>45240</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45072</v>
+        <v>45371</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4995,148 +4995,221 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
+          <t>A 19295-2025</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="n">
+        <v>45769</v>
+      </c>
+      <c r="E54" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>S 921-2025</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D54" s="1" t="n">
+      <c r="D55" s="1" t="n">
         <v>45737</v>
       </c>
-      <c r="E54" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
+      <c r="E55" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
         <v>0.3</v>
       </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>S 14-2026</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D55" s="1" t="n">
+      <c r="D56" s="1" t="n">
         <v>46028</v>
       </c>
-      <c r="E55" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" s="2" t="inlineStr"/>
+      <c r="E56" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>45212</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 46384-2025</t>
+          <t>A 46379-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1269,14 +1269,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
         <v>45925</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
         <v>2</v>
@@ -1298,7 +1298,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1313,7 +1313,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1322,377 +1322,377 @@
         <v>2</v>
       </c>
       <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
         <v>3</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 48265-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45933</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Timmerticka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 23796-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Vitplätt
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 46384-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Duvhök
 Tjäder</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46384-2025 artfynd.xlsx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46384-2025 karta.png", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46384-2025 georefererad karta.tif", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46384-2025 FSC-klagomål.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46384-2025 FSC-klagomål mail.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46384-2025 tillsynsbegäran.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46384-2025 tillsynsbegäran mail.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46384-2025 prioriterade fågelarter.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 48265-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45933</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Timmerticka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 46379-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45925</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Fiskgjuse</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 23796-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46164</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Vitplätt
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
         <v/>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 26650-2022</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44739</v>
+        <v>45337</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2717,7 +2717,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 26650-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44564</v>
+        <v>44739</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45441</v>
+        <v>45371</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45567</v>
+        <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2953,7 +2953,7 @@
         <v>45734</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45378</v>
+        <v>45567</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46078</v>
+        <v>45441</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3111,13 +3111,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3160,7 +3155,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3174,10 +3169,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46078</v>
+        <v>45127</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3189,13 +3184,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3238,7 +3228,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3252,10 +3242,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46078</v>
+        <v>45880</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3267,13 +3257,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3316,7 +3301,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3330,10 +3315,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45127</v>
+        <v>45240</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3346,7 +3331,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3389,7 +3374,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3403,10 +3388,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45880</v>
+        <v>45769</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3419,7 +3404,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3462,7 +3447,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3476,10 +3461,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45645</v>
+        <v>44977</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3492,7 +3477,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6.6</v>
+        <v>3.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3535,7 +3520,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3549,10 +3534,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45782</v>
+        <v>45644</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3565,7 +3550,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3608,7 +3593,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3622,10 +3607,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45072</v>
+        <v>45645</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3638,7 +3623,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.9</v>
+        <v>6.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3681,7 +3666,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3695,10 +3680,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46196</v>
+        <v>45782</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3711,7 +3696,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3754,7 +3739,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3768,10 +3753,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45271</v>
+        <v>45378</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3784,7 +3769,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3844,7 +3829,7 @@
         <v>45321</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3900,7 +3885,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3914,10 +3899,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44586</v>
+        <v>45659</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3930,7 +3915,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3973,7 +3958,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3987,10 +3972,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45337</v>
+        <v>45371</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4003,7 +3988,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4046,7 +4031,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4060,10 +4045,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46261</v>
+        <v>44586</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4076,7 +4061,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4119,7 +4104,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4133,10 +4118,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45659</v>
+        <v>46196</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4149,7 +4134,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4192,7 +4177,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4206,10 +4191,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44977</v>
+        <v>45084</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4222,7 +4207,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4265,7 +4250,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4279,10 +4264,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46230</v>
+        <v>46078</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4294,8 +4279,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>7.6</v>
+        <v>1.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4338,7 +4328,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4352,10 +4342,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46281</v>
+        <v>46078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4367,8 +4357,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4411,7 +4406,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4421,14 +4416,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46239</v>
+        <v>46078</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4440,8 +4435,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46244</v>
+        <v>46261</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45644</v>
+        <v>45271</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45371</v>
+        <v>45072</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 41561-2026</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46301</v>
+        <v>46230</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>7.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45084</v>
+        <v>46281</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4859,14 +4859,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45240</v>
+        <v>46239</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45371</v>
+        <v>46244</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 41561-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45769</v>
+        <v>46301</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5085,7 +5085,7 @@
         <v>45737</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>46028</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>45212</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 46379-2025</t>
+          <t>A 48265-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1269,14 +1269,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45925</v>
+        <v>45933</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1322,157 +1322,157 @@
         <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
         <v>3</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
+          <t>Timmerticka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 46379-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>Spillkråka
 Fiskgjuse</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 48265-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45933</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Timmerticka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
         <v/>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
         <v>46164</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 44926-2025</t>
+          <t>A 34574-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45918</v>
+        <v>45847</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.8</v>
+        <v>7.4</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1984,46 +1984,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2842-2025</t>
+          <t>A 6042-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2037,10 +2037,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45677</v>
+        <v>45336</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2053,13 +2053,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2086,53 +2086,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 34574-2025</t>
+          <t>A 44926-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2146,10 +2142,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45847</v>
+        <v>45918</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2162,7 +2158,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.4</v>
+        <v>3.8</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2198,46 +2194,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6042-2024</t>
+          <t>A 2842-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2251,10 +2247,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45336</v>
+        <v>45677</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2267,13 +2263,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2300,42 +2296,46 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
         <v/>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 26650-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45337</v>
+        <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2717,7 +2717,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 26650-2022</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44739</v>
+        <v>44564</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45371</v>
+        <v>45441</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44564</v>
+        <v>45567</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45734</v>
+        <v>45378</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3009,7 +3009,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45567</v>
+        <v>45734</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45441</v>
+        <v>45127</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3155,7 +3155,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45127</v>
+        <v>45880</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45880</v>
+        <v>45072</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3301,7 +3301,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45240</v>
+        <v>45271</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3374,7 +3374,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45769</v>
+        <v>45321</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44977</v>
+        <v>44586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3520,7 +3520,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45644</v>
+        <v>45337</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3610,7 +3610,7 @@
         <v>45645</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45782</v>
+        <v>45659</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3739,7 +3739,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45378</v>
+        <v>44977</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3812,7 +3812,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45321</v>
+        <v>46078</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3841,8 +3841,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3885,7 +3890,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3899,10 +3904,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45659</v>
+        <v>46078</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3914,8 +3919,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3958,7 +3968,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3972,10 +3982,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45371</v>
+        <v>46078</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3987,8 +3997,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4031,7 +4046,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4045,10 +4060,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44586</v>
+        <v>45644</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4104,7 +4119,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4118,10 +4133,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46196</v>
+        <v>45782</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4134,7 +4149,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4177,7 +4192,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4191,10 +4206,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45084</v>
+        <v>45371</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4207,7 +4222,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4250,7 +4265,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4264,10 +4279,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46078</v>
+        <v>46196</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4279,13 +4294,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4328,7 +4338,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4342,10 +4352,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46078</v>
+        <v>45084</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4357,13 +4367,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4406,7 +4411,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4420,10 +4425,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46078</v>
+        <v>45240</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4435,13 +4440,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46261</v>
+        <v>46230</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>7.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45271</v>
+        <v>45371</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45072</v>
+        <v>45769</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46230</v>
+        <v>46281</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>7.6</v>
+        <v>1.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4786,14 +4786,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46281</v>
+        <v>46239</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4859,14 +4859,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 41561-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46244</v>
+        <v>46301</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 41561-2026</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46301</v>
+        <v>46261</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45737</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>46028</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>45212</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 48265-2025</t>
+          <t>A 46379-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1269,14 +1269,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45933</v>
+        <v>45925</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1322,157 +1322,157 @@
         <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U8" t="n">
         <v>3</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
+          <t>Spillkråka
+Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 48265-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45933</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>Timmerticka
 Tjäder</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 46379-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45925</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Fiskgjuse</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
         <v/>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
         <v>46164</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 34574-2025</t>
+          <t>A 44926-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45847</v>
+        <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>7.4</v>
+        <v>3.8</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1984,46 +1984,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 6042-2024</t>
+          <t>A 2842-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2037,10 +2037,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45336</v>
+        <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2053,13 +2053,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2086,49 +2086,53 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 44926-2025</t>
+          <t>A 34574-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2142,10 +2146,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45918</v>
+        <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2158,7 +2162,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.8</v>
+        <v>7.4</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2194,46 +2198,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 2842-2025</t>
+          <t>A 6042-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2247,10 +2251,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45677</v>
+        <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2263,13 +2267,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2296,46 +2300,42 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 3673-2022</t>
+          <t>A 23877-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44586</v>
+        <v>44722</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2571,7 +2571,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 23877-2022</t>
+          <t>A 3673-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44722</v>
+        <v>44586</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2661,7 +2661,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44564</v>
+        <v>45371</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45441</v>
+        <v>44564</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45567</v>
+        <v>45337</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45378</v>
+        <v>45271</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3009,7 +3009,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45734</v>
+        <v>45072</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45127</v>
+        <v>45734</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3155,7 +3155,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45880</v>
+        <v>45567</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3228,7 +3228,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45072</v>
+        <v>45441</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3301,7 +3301,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45271</v>
+        <v>45240</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3374,7 +3374,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45321</v>
+        <v>44977</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44586</v>
+        <v>45769</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3520,7 +3520,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45337</v>
+        <v>45644</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45645</v>
+        <v>45659</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>6.6</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3666,7 +3666,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45659</v>
+        <v>45378</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3739,7 +3739,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44977</v>
+        <v>45321</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3812,7 +3812,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46078</v>
+        <v>45127</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3841,13 +3841,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3890,7 +3885,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3904,10 +3899,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46078</v>
+        <v>45880</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3919,13 +3914,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3968,7 +3958,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3982,10 +3972,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46078</v>
+        <v>45371</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3997,13 +3987,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4046,7 +4031,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4060,10 +4045,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45644</v>
+        <v>44586</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4119,7 +4104,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4133,10 +4118,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45782</v>
+        <v>45084</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4149,7 +4134,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4192,7 +4177,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4206,10 +4191,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45371</v>
+        <v>45645</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4222,7 +4207,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>6.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4265,7 +4250,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4279,10 +4264,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46196</v>
+        <v>46078</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4294,8 +4279,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4338,7 +4328,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4352,10 +4342,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45084</v>
+        <v>46078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4367,8 +4357,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4411,7 +4406,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4425,10 +4420,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45240</v>
+        <v>46078</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4440,8 +4435,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46230</v>
+        <v>45782</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>7.6</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45371</v>
+        <v>46196</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45769</v>
+        <v>46230</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.8</v>
+        <v>7.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4720,7 +4720,7 @@
         <v>46281</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>46239</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>46244</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>46301</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>46261</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45737</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>46028</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>45212</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45925</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>45933</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>46164</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44722</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44586</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>45371</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>44564</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>45337</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>45271</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>45072</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45734</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>45567</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>45441</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>45240</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>44977</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45769</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>45644</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>45659</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>45378</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45321</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>45127</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>45880</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>45371</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44586</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>45084</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>45645</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>46078</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>46078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>46078</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>45782</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>46196</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>46230</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>46281</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>46239</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>46244</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>46301</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>46261</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45737</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>46028</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>45212</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45925</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>45933</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>46164</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44722</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44586</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>45371</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>44564</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>45337</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>45271</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>45072</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45734</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>45567</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>45441</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>45240</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>44977</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45769</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>45644</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>45659</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>45378</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45321</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>45127</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>45880</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>45371</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44586</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>45084</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>45645</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>46078</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>46078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>46078</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>45782</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>46196</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>46230</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>46281</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>46239</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>46244</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>46301</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>46261</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45737</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>46028</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 49789-2023</t>
+          <t>A 62768-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45212</v>
+        <v>46008</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,13 +1073,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1106,593 +1106,593 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 62768-2025 artfynd.xlsx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 62768-2025 karta.png", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 62768-2025 georefererad karta.tif", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 62768-2025 FSC-klagomål.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 62768-2025 FSC-klagomål mail.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 62768-2025 tillsynsbegäran.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 62768-2025 tillsynsbegäran mail.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 62768-2025 prioriterade fågelarter.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 48265-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45933</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>2</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Timmerticka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 46379-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 23796-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Vitplätt
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 46384-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Duvhök
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46384-2025 artfynd.xlsx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46384-2025 karta.png", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46384-2025 georefererad karta.tif", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46384-2025 FSC-klagomål.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46384-2025 FSC-klagomål mail.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46384-2025 tillsynsbegäran.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46384-2025 tillsynsbegäran mail.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46384-2025 prioriterade fågelarter.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 49789-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45212</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Klippfrullania
 Trubbfjädermossa</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 62768-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46008</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>4</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 62768-2025 artfynd.xlsx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 62768-2025 karta.png", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 62768-2025 georefererad karta.tif", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 62768-2025 FSC-klagomål.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 62768-2025 FSC-klagomål mail.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 62768-2025 tillsynsbegäran.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 62768-2025 tillsynsbegäran mail.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 62768-2025 prioriterade fågelarter.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 46379-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45925</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Fiskgjuse</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 48265-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45933</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Timmerticka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 23796-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46164</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Vitplätt
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 46384-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45925</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Duvhök
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46384-2025 artfynd.xlsx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46384-2025 karta.png", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46384-2025 georefererad karta.tif", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46384-2025 FSC-klagomål.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46384-2025 FSC-klagomål mail.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46384-2025 tillsynsbegäran.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46384-2025 tillsynsbegäran mail.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46384-2025 prioriterade fågelarter.docx", "A 46384-2025")</f>
         <v/>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 23877-2022</t>
+          <t>A 3673-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44722</v>
+        <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2571,7 +2571,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3673-2022</t>
+          <t>A 23877-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44586</v>
+        <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2661,7 +2661,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45371</v>
+        <v>45734</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44564</v>
+        <v>45084</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45337</v>
+        <v>45240</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45271</v>
+        <v>44564</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3009,7 +3009,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45072</v>
+        <v>45371</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45734</v>
+        <v>45769</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3155,7 +3155,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45567</v>
+        <v>46196</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3228,7 +3228,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45441</v>
+        <v>46230</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.8</v>
+        <v>7.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3301,7 +3301,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45240</v>
+        <v>45645</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>6.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3374,7 +3374,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44977</v>
+        <v>46281</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3457,14 +3457,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45769</v>
+        <v>46239</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3520,7 +3520,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45644</v>
+        <v>46244</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45659</v>
+        <v>45127</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3666,7 +3666,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45378</v>
+        <v>45880</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45321</v>
+        <v>46078</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3768,8 +3768,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3812,7 +3817,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3826,10 +3831,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45127</v>
+        <v>46078</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3841,8 +3846,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3885,7 +3895,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3899,10 +3909,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45880</v>
+        <v>46078</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3914,8 +3924,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3958,7 +3973,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 41561-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3972,10 +3987,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45371</v>
+        <v>46301</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3988,7 +4003,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4031,7 +4046,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4045,10 +4060,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44586</v>
+        <v>46261</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4061,7 +4076,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4104,7 +4119,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4118,10 +4133,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45084</v>
+        <v>45441</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4134,7 +4149,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4177,7 +4192,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4191,10 +4206,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45645</v>
+        <v>45567</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4207,7 +4222,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.6</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4250,7 +4265,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4264,10 +4279,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46078</v>
+        <v>45378</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4279,13 +4294,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4328,7 +4338,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4342,10 +4352,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46078</v>
+        <v>45782</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4357,13 +4367,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4406,7 +4411,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4420,10 +4425,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46078</v>
+        <v>45072</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4435,13 +4440,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45782</v>
+        <v>45271</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46196</v>
+        <v>45321</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46230</v>
+        <v>44586</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>7.6</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46281</v>
+        <v>45337</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4786,14 +4786,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46239</v>
+        <v>45659</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46244</v>
+        <v>44977</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 41561-2026</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46301</v>
+        <v>45644</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46261</v>
+        <v>45371</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5085,7 +5085,7 @@
         <v>45737</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>46028</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE56"/>
+  <dimension ref="A1:AE57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46008</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 48265-2025</t>
+          <t>A 49789-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45933</v>
+        <v>45212</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1183,13 +1183,13 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1216,483 +1216,483 @@
         <v>2</v>
       </c>
       <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Klippfrullania
+Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 46379-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
         <v>3</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 48265-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45933</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Timmerticka
 Tjäder</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 46379-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 23796-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45925</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J8" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
         <v>2</v>
       </c>
-      <c r="T8" t="n">
-        <v>4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Fiskgjuse</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 23796-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46164</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Vitplätt
 Tjäder</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 46384-2025</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D11" s="1" t="n">
         <v>45925</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>3.1</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>2</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Duvhök
 Tjäder</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46384-2025 artfynd.xlsx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46384-2025 karta.png", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46384-2025 georefererad karta.tif", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46384-2025 FSC-klagomål.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46384-2025 FSC-klagomål mail.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46384-2025 tillsynsbegäran.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46384-2025 tillsynsbegäran mail.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46384-2025 prioriterade fågelarter.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 49789-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45212</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Klippfrullania
-Trubbfjädermossa</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
         <v/>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45734</v>
+        <v>45337</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45084</v>
+        <v>45371</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45240</v>
+        <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44564</v>
+        <v>45645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>6.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3009,7 +3009,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45371</v>
+        <v>45734</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45769</v>
+        <v>45127</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3155,7 +3155,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46196</v>
+        <v>45880</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3228,7 +3228,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46230</v>
+        <v>44977</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>7.6</v>
+        <v>3.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3301,7 +3301,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45645</v>
+        <v>45644</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6.6</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3374,7 +3374,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46281</v>
+        <v>46078</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3403,8 +3403,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3447,7 +3452,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3457,14 +3462,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46239</v>
+        <v>46078</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3476,8 +3481,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3520,7 +3530,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3534,10 +3544,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46244</v>
+        <v>46078</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3549,8 +3559,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3593,7 +3608,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3607,10 +3622,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45127</v>
+        <v>45659</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3623,7 +3638,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3666,7 +3681,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3680,10 +3695,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45880</v>
+        <v>45567</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3696,7 +3711,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3739,7 +3754,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3753,10 +3768,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46078</v>
+        <v>45441</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3768,13 +3783,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3817,7 +3827,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3831,10 +3841,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46078</v>
+        <v>45240</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3846,13 +3856,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3895,7 +3900,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3909,10 +3914,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46078</v>
+        <v>45782</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3924,13 +3929,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 41561-2026</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46301</v>
+        <v>45769</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46261</v>
+        <v>45378</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45441</v>
+        <v>45321</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45567</v>
+        <v>46196</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45378</v>
+        <v>45371</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45782</v>
+        <v>44586</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45072</v>
+        <v>45084</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45271</v>
+        <v>46230</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>7.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45321</v>
+        <v>46281</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4640,14 +4640,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44586</v>
+        <v>46239</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45337</v>
+        <v>45271</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45659</v>
+        <v>46244</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44977</v>
+        <v>45072</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 41561-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45644</v>
+        <v>46301</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45371</v>
+        <v>46261</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5085,7 +5085,7 @@
         <v>45737</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="V55" s="2" t="inlineStr"/>
     </row>
-    <row r="56">
+    <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
           <t>S 14-2026</t>
@@ -5158,58 +5158,131 @@
         <v>46028</v>
       </c>
       <c r="E56" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>S 2660-2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="n">
         <v>46308</v>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" s="2" t="inlineStr"/>
+      <c r="E57" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 62768-2025</t>
+          <t>A 49789-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46008</v>
+        <v>45212</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,13 +1073,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1106,160 +1106,160 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Klippfrullania
+Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 62768-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
         <v>4</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>4</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Tjäder</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 62768-2025 artfynd.xlsx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 62768-2025 karta.png", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 62768-2025 georefererad karta.tif", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 62768-2025 FSC-klagomål.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 62768-2025 FSC-klagomål mail.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 62768-2025 tillsynsbegäran.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 62768-2025 tillsynsbegäran mail.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 62768-2025 prioriterade fågelarter.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 49789-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45212</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Klippfrullania
-Trubbfjädermossa</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 46379-2025</t>
+          <t>A 48265-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1269,14 +1269,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45925</v>
+        <v>45933</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1322,157 +1322,157 @@
         <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
         <v>3</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
+          <t>Timmerticka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 46379-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>Spillkråka
 Fiskgjuse</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 48265-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45933</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Timmerticka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
         <v/>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
         <v>46164</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 44926-2025</t>
+          <t>A 2842-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45918</v>
+        <v>45677</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1981,49 +1981,53 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2842-2025</t>
+          <t>A 34574-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2037,10 +2041,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45677</v>
+        <v>45847</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2053,7 +2057,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2086,53 +2090,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 34574-2025</t>
+          <t>A 6042-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45847</v>
+        <v>45336</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2162,13 +2162,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.4</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2202,42 +2202,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6042-2024</t>
+          <t>A 44926-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45336</v>
+        <v>45918</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2303,39 +2303,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45337</v>
+        <v>44564</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45371</v>
+        <v>45072</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44564</v>
+        <v>45734</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45645</v>
+        <v>45271</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3009,7 +3009,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45734</v>
+        <v>45127</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45127</v>
+        <v>45880</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45880</v>
+        <v>46078</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3184,8 +3184,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3228,7 +3233,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3242,10 +3247,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44977</v>
+        <v>46078</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3257,8 +3262,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3301,7 +3311,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3315,10 +3325,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45644</v>
+        <v>46078</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3330,8 +3340,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3374,7 +3389,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3388,10 +3403,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46078</v>
+        <v>45441</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3403,13 +3418,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3452,7 +3462,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3466,10 +3476,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46078</v>
+        <v>45567</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3481,13 +3491,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3530,7 +3535,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3544,10 +3549,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46078</v>
+        <v>45378</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3559,13 +3564,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45659</v>
+        <v>45321</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45567</v>
+        <v>44586</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45441</v>
+        <v>45337</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45240</v>
+        <v>45645</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>6.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45782</v>
+        <v>45659</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45769</v>
+        <v>45782</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45378</v>
+        <v>44977</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45321</v>
+        <v>46196</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46196</v>
+        <v>45644</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45371</v>
+        <v>46230</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.7</v>
+        <v>7.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44586</v>
+        <v>46281</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4421,14 +4421,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45084</v>
+        <v>46239</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46230</v>
+        <v>45371</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>7.6</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46281</v>
+        <v>46244</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4640,14 +4640,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46239</v>
+        <v>45084</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45271</v>
+        <v>45240</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 41561-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46244</v>
+        <v>46301</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45072</v>
+        <v>45371</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 41561-2026</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46301</v>
+        <v>45769</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>46261</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45737</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>46028</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>46308</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>45212</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 48265-2025</t>
+          <t>A 46379-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1269,14 +1269,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45933</v>
+        <v>45925</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1322,157 +1322,157 @@
         <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U8" t="n">
         <v>3</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
+          <t>Spillkråka
+Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 48265-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45933</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>Timmerticka
 Tjäder</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 46379-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45925</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Fiskgjuse</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
         <v/>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
         <v>46164</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45677</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>45847</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45336</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45918</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44564</v>
+        <v>45337</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45072</v>
+        <v>45371</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45734</v>
+        <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45271</v>
+        <v>45734</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3026,7 +3026,7 @@
         <v>45127</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45880</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46078</v>
+        <v>45567</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3184,13 +3184,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3233,7 +3228,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3247,10 +3242,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46078</v>
+        <v>45441</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3262,13 +3257,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3311,7 +3301,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3325,10 +3315,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46078</v>
+        <v>45240</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3340,13 +3330,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3389,7 +3374,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3403,10 +3388,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45441</v>
+        <v>44977</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3419,7 +3404,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3462,7 +3447,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3476,10 +3461,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45567</v>
+        <v>45644</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3492,7 +3477,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3535,7 +3520,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3549,10 +3534,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45378</v>
+        <v>45769</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3565,7 +3550,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3608,7 +3593,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3622,10 +3607,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45321</v>
+        <v>45659</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3638,7 +3623,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3681,7 +3666,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3695,10 +3680,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44586</v>
+        <v>45378</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3711,7 +3696,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3754,7 +3739,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3768,10 +3753,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45337</v>
+        <v>45321</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3784,7 +3769,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3827,7 +3812,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3841,10 +3826,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45645</v>
+        <v>45782</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3857,7 +3842,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.6</v>
+        <v>2.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3900,7 +3885,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3914,10 +3899,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45659</v>
+        <v>45371</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3930,7 +3915,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3973,7 +3958,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3987,10 +3972,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45782</v>
+        <v>44586</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4003,7 +3988,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4046,7 +4031,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4060,10 +4045,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44977</v>
+        <v>45084</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4076,7 +4061,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4136,7 +4121,7 @@
         <v>46196</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4192,7 +4177,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4206,10 +4191,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45644</v>
+        <v>45271</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4222,7 +4207,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4282,7 +4267,7 @@
         <v>46230</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4338,7 +4323,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4352,10 +4337,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46281</v>
+        <v>45072</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4368,7 +4353,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4411,7 +4396,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4421,14 +4406,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46239</v>
+        <v>46281</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4441,7 +4426,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4484,7 +4469,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4494,14 +4479,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45371</v>
+        <v>46239</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4514,7 +4499,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4574,7 +4559,7 @@
         <v>46244</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4630,7 +4615,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4644,10 +4629,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45084</v>
+        <v>45645</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4660,7 +4645,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>6.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4703,7 +4688,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 41561-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4717,10 +4702,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45240</v>
+        <v>46301</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4733,7 +4718,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4776,7 +4761,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 41561-2026</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4790,10 +4775,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46301</v>
+        <v>46261</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4849,7 +4834,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4863,10 +4848,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45371</v>
+        <v>46078</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4878,8 +4863,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4922,7 +4912,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4936,10 +4926,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45769</v>
+        <v>46078</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4951,8 +4941,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4995,7 +4990,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5009,10 +5004,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46261</v>
+        <v>46078</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5024,8 +5019,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5085,7 +5085,7 @@
         <v>45737</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>46028</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>46308</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>45212</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 46379-2025</t>
+          <t>A 48265-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1269,14 +1269,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45925</v>
+        <v>45933</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1322,157 +1322,157 @@
         <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
         <v>3</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
+          <t>Timmerticka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 46379-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46312</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>Spillkråka
 Fiskgjuse</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 48265-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45933</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46311</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Timmerticka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
         <v/>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
         <v>46164</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 2842-2025</t>
+          <t>A 44926-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45677</v>
+        <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1981,53 +1981,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 34574-2025</t>
+          <t>A 2842-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2041,10 +2037,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45847</v>
+        <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2057,7 +2053,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2090,49 +2086,53 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 6042-2024</t>
+          <t>A 34574-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45336</v>
+        <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2162,13 +2162,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>7.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2202,42 +2202,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 44926-2025</t>
+          <t>A 6042-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45918</v>
+        <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2303,39 +2303,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45337</v>
+        <v>44564</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45371</v>
+        <v>45441</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44564</v>
+        <v>45567</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45734</v>
+        <v>45378</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3009,7 +3009,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45127</v>
+        <v>45734</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45880</v>
+        <v>45072</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3155,7 +3155,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45567</v>
+        <v>45271</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3228,7 +3228,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45441</v>
+        <v>45321</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3301,7 +3301,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45240</v>
+        <v>44586</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3374,7 +3374,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44977</v>
+        <v>45337</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45644</v>
+        <v>45782</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3520,7 +3520,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45769</v>
+        <v>45645</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.8</v>
+        <v>6.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3610,7 +3610,7 @@
         <v>45659</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45378</v>
+        <v>44977</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3739,7 +3739,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45321</v>
+        <v>46078</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3768,8 +3768,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3812,7 +3817,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3826,10 +3831,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45782</v>
+        <v>46078</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3841,8 +3846,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3885,7 +3895,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3899,10 +3909,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45371</v>
+        <v>46078</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3914,8 +3924,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3958,7 +3973,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3972,10 +3987,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44586</v>
+        <v>46196</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3988,7 +4003,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4031,7 +4046,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4045,10 +4060,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45084</v>
+        <v>45644</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4061,7 +4076,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4104,7 +4119,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4118,10 +4133,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46196</v>
+        <v>45371</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4134,7 +4149,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4177,7 +4192,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4191,10 +4206,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45271</v>
+        <v>46230</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4207,7 +4222,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>7.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4250,7 +4265,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4264,10 +4279,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46230</v>
+        <v>46281</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4280,7 +4295,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>7.6</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4323,7 +4338,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4333,14 +4348,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45072</v>
+        <v>46239</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4353,7 +4368,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4396,7 +4411,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4410,10 +4425,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46281</v>
+        <v>45084</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4426,7 +4441,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4469,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4479,14 +4494,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4499,7 +4514,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4542,7 +4557,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4556,10 +4571,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46244</v>
+        <v>45240</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4572,7 +4587,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4615,7 +4630,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4629,10 +4644,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45645</v>
+        <v>45371</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4645,7 +4660,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>6.6</v>
+        <v>2.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4688,7 +4703,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 41561-2026</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4702,10 +4717,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46301</v>
+        <v>45769</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4718,7 +4733,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4761,7 +4776,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 41561-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4775,10 +4790,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46261</v>
+        <v>46301</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4834,7 +4849,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4848,10 +4863,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46078</v>
+        <v>46261</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4863,13 +4878,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4912,7 +4922,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4926,10 +4936,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46078</v>
+        <v>45127</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4941,13 +4951,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4990,7 +4995,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5004,10 +5009,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46078</v>
+        <v>45880</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5019,13 +5024,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5085,7 +5085,7 @@
         <v>45737</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>46028</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>46308</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>45212</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45933</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>45925</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>46164</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>44564</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>45441</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>45567</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>45378</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>45734</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45072</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>45271</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>45321</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>44586</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>45337</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45782</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>45645</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>45659</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>44977</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>46078</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>46078</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>46078</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>46196</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>45644</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45371</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>46230</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>46281</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>46239</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>45084</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>46244</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>45240</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>45371</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>45769</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>46301</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>46261</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45127</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45880</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45737</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>46028</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>46308</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>45212</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45933</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>45925</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>46164</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>44564</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>45441</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>45567</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>45378</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>45734</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45072</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>45271</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>45321</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>44586</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>45337</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45782</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>45645</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>45659</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>44977</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>46078</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>46078</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>46078</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>46196</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>45644</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45371</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>46230</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>46281</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>46239</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>45084</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>46244</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>45240</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>45371</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>45769</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>46301</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>46261</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45127</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45880</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45737</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>46028</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>46308</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 49789-2023</t>
+          <t>A 62768-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45212</v>
+        <v>46008</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,13 +1073,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1106,160 +1106,160 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 62768-2025 artfynd.xlsx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 62768-2025 karta.png", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 62768-2025 georefererad karta.tif", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 62768-2025 FSC-klagomål.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 62768-2025 FSC-klagomål mail.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 62768-2025 tillsynsbegäran.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 62768-2025 tillsynsbegäran mail.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 62768-2025 prioriterade fågelarter.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 49789-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45212</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Klippfrullania
 Trubbfjädermossa</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 62768-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46008</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>4</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 62768-2025 artfynd.xlsx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 62768-2025 karta.png", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 62768-2025 georefererad karta.tif", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 62768-2025 FSC-klagomål.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 62768-2025 FSC-klagomål mail.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 62768-2025 tillsynsbegäran.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 62768-2025 tillsynsbegäran mail.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 62768-2025 prioriterade fågelarter.docx", "A 62768-2025")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 48265-2025</t>
+          <t>A 46379-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1269,14 +1269,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45933</v>
+        <v>45925</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1322,157 +1322,157 @@
         <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U8" t="n">
         <v>3</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
+          <t>Spillkråka
+Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 48265-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45933</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>Timmerticka
 Tjäder</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 46379-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45925</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Fiskgjuse</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
         <v/>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
         <v>46164</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44564</v>
+        <v>45337</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45441</v>
+        <v>45371</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45567</v>
+        <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45378</v>
+        <v>44977</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3009,7 +3009,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45734</v>
+        <v>45644</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45072</v>
+        <v>45734</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3155,7 +3155,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45271</v>
+        <v>45659</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3228,7 +3228,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45321</v>
+        <v>45782</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3301,7 +3301,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44586</v>
+        <v>45645</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>6.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3374,7 +3374,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45337</v>
+        <v>45567</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45782</v>
+        <v>45441</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3520,7 +3520,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45645</v>
+        <v>45240</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6.6</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45659</v>
+        <v>45769</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3666,7 +3666,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44977</v>
+        <v>46078</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3695,8 +3695,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3756,7 +3761,7 @@
         <v>46078</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3817,7 +3822,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3834,7 +3839,7 @@
         <v>46078</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3852,7 +3857,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3895,7 +3900,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3909,10 +3914,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46078</v>
+        <v>46196</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3924,13 +3929,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46196</v>
+        <v>45378</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45644</v>
+        <v>45321</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4136,7 +4136,7 @@
         <v>45371</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46230</v>
+        <v>44586</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>7.6</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46281</v>
+        <v>45084</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4348,14 +4348,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46239</v>
+        <v>46230</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>7.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45084</v>
+        <v>46281</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4494,14 +4494,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46244</v>
+        <v>46239</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45240</v>
+        <v>45271</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45371</v>
+        <v>46244</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45769</v>
+        <v>45072</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4793,7 +4793,7 @@
         <v>46301</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>46261</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45127</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45880</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45737</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>46028</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>46308</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46008</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>45212</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 46379-2025</t>
+          <t>A 48265-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1269,14 +1269,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45925</v>
+        <v>45933</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1322,377 +1322,377 @@
         <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
         <v>3</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
+          <t>Timmerticka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 23796-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Vitplätt
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 46384-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Duvhök
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46384-2025 artfynd.xlsx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46384-2025 karta.png", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46384-2025 georefererad karta.tif", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46384-2025 FSC-klagomål.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46384-2025 FSC-klagomål mail.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46384-2025 tillsynsbegäran.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46384-2025 tillsynsbegäran mail.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46384-2025 prioriterade fågelarter.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 46379-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>Spillkråka
 Fiskgjuse</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 48265-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45933</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Timmerticka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 23796-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46164</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Vitplätt
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 46384-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45925</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Duvhök
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46384-2025 artfynd.xlsx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46384-2025 karta.png", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46384-2025 georefererad karta.tif", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46384-2025 FSC-klagomål.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46384-2025 FSC-klagomål mail.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46384-2025 tillsynsbegäran.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46384-2025 tillsynsbegäran mail.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46384-2025 prioriterade fågelarter.docx", "A 46384-2025")</f>
         <v/>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45337</v>
+        <v>44564</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45371</v>
+        <v>45734</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44564</v>
+        <v>45645</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>6.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44977</v>
+        <v>45441</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3009,7 +3009,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45644</v>
+        <v>45567</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45734</v>
+        <v>45378</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3155,7 +3155,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45659</v>
+        <v>46078</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3182,6 +3182,11 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -3228,7 +3233,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3242,10 +3247,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45782</v>
+        <v>46078</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3257,8 +3262,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3301,7 +3311,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3315,10 +3325,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45645</v>
+        <v>46078</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3330,8 +3340,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3374,7 +3389,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3388,10 +3403,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45567</v>
+        <v>45127</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3404,7 +3419,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3447,7 +3462,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3461,10 +3476,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45441</v>
+        <v>45880</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3477,7 +3492,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3520,7 +3535,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3534,10 +3549,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45240</v>
+        <v>45072</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3550,7 +3565,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3593,7 +3608,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3607,10 +3622,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45769</v>
+        <v>45271</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3623,7 +3638,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3666,7 +3681,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3680,10 +3695,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46078</v>
+        <v>45321</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3695,13 +3710,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3744,7 +3754,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3758,10 +3768,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46078</v>
+        <v>45782</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3773,13 +3783,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3822,7 +3827,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3836,10 +3841,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46078</v>
+        <v>44586</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3851,13 +3856,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46196</v>
+        <v>45337</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45378</v>
+        <v>46196</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45321</v>
+        <v>45659</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45371</v>
+        <v>44977</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44586</v>
+        <v>46230</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>7.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45084</v>
+        <v>46281</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4348,14 +4348,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46230</v>
+        <v>46239</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46281</v>
+        <v>45644</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4494,14 +4494,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45271</v>
+        <v>45371</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 41561-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46244</v>
+        <v>46301</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45072</v>
+        <v>46261</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 41561-2026</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46301</v>
+        <v>45084</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46261</v>
+        <v>45240</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45127</v>
+        <v>45371</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45880</v>
+        <v>45769</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5085,7 +5085,7 @@
         <v>45737</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>46028</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>46308</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE57"/>
+  <dimension ref="A1:AE58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46008</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>45212</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45933</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>45925</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44564</v>
+        <v>45337</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45734</v>
+        <v>45371</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45645</v>
+        <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.6</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45441</v>
+        <v>45645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.8</v>
+        <v>6.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3009,7 +3009,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45567</v>
+        <v>45734</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45378</v>
+        <v>45127</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46078</v>
+        <v>45880</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3184,13 +3184,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3233,7 +3228,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3247,10 +3242,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46078</v>
+        <v>44977</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3262,13 +3257,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3311,7 +3301,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3325,10 +3315,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46078</v>
+        <v>45644</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3340,13 +3330,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3389,7 +3374,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3403,10 +3388,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45127</v>
+        <v>45659</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3419,7 +3404,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3462,7 +3447,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3476,10 +3461,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45880</v>
+        <v>46078</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3491,8 +3476,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3535,7 +3525,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3549,10 +3539,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45072</v>
+        <v>46078</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3564,8 +3554,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3608,7 +3603,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3622,10 +3617,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45271</v>
+        <v>46078</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3637,8 +3632,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45321</v>
+        <v>45567</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45782</v>
+        <v>45441</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44586</v>
+        <v>45240</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45337</v>
+        <v>45769</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46196</v>
+        <v>45782</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45659</v>
+        <v>45378</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44977</v>
+        <v>45321</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46230</v>
+        <v>46196</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>7.6</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46281</v>
+        <v>45371</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4348,14 +4348,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46239</v>
+        <v>44586</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45644</v>
+        <v>45084</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46244</v>
+        <v>46230</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>7.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45371</v>
+        <v>46281</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 41561-2026</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4640,14 +4640,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46301</v>
+        <v>46239</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46261</v>
+        <v>45271</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45084</v>
+        <v>46244</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45240</v>
+        <v>45072</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 41561-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45371</v>
+        <v>46301</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45769</v>
+        <v>46261</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5068,24 +5068,24 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S 921-2025</t>
+          <t>A 43672-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45737</v>
+        <v>46316</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5141,148 +5141,221 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
+          <t>S 921-2025</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>45737</v>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>S 14-2026</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D56" s="1" t="n">
+      <c r="D57" s="1" t="n">
         <v>46028</v>
       </c>
-      <c r="E56" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="E57" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>S 2660-2026</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D57" s="1" t="n">
+      <c r="D58" s="1" t="n">
         <v>46308</v>
       </c>
-      <c r="E57" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" s="2" t="inlineStr"/>
+      <c r="E58" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>46008</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>45212</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 48265-2025</t>
+          <t>A 46379-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1269,14 +1269,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45933</v>
+        <v>45925</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1322,377 +1322,377 @@
         <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U8" t="n">
         <v>3</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
+          <t>Spillkråka
+Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 48265-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45933</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>Timmerticka
 Tjäder</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 23796-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D10" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>3.6</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>2</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>2</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Vitplätt
 Tjäder</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 46384-2025</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D11" s="1" t="n">
         <v>45925</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>3.1</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>2</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Duvhök
 Tjäder</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46384-2025 artfynd.xlsx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46384-2025 karta.png", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46384-2025 georefererad karta.tif", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46384-2025 FSC-klagomål.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46384-2025 FSC-klagomål mail.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46384-2025 tillsynsbegäran.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46384-2025 tillsynsbegäran mail.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46384-2025 prioriterade fågelarter.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 46379-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45925</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Fiskgjuse</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
         <v/>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 44926-2025</t>
+          <t>A 2842-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45918</v>
+        <v>45677</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1981,49 +1981,53 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2842-2025</t>
+          <t>A 34574-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2037,10 +2041,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45677</v>
+        <v>45847</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2053,7 +2057,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2086,53 +2090,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 34574-2025</t>
+          <t>A 6042-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45847</v>
+        <v>45336</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2162,13 +2162,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.4</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2202,42 +2202,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6042-2024</t>
+          <t>A 44926-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45336</v>
+        <v>45918</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2303,39 +2303,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 23877-2022</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44722</v>
+        <v>44564</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2644,7 +2644,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 26650-2022</t>
+          <t>A 23877-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44739</v>
+        <v>44722</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 26650-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45337</v>
+        <v>44739</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45371</v>
+        <v>44977</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44564</v>
+        <v>45734</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45645</v>
+        <v>45644</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6.6</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3009,7 +3009,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45734</v>
+        <v>45127</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45127</v>
+        <v>45880</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45880</v>
+        <v>45371</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3228,7 +3228,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44977</v>
+        <v>45084</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3301,7 +3301,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45644</v>
+        <v>45240</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3374,7 +3374,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45659</v>
+        <v>45645</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.4</v>
+        <v>6.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46078</v>
+        <v>45782</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3476,13 +3476,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3525,7 +3520,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3539,10 +3534,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46078</v>
+        <v>45371</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3554,13 +3549,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3603,7 +3593,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3617,10 +3607,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46078</v>
+        <v>45769</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3632,13 +3622,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3681,7 +3666,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3695,10 +3680,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45567</v>
+        <v>45441</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3711,7 +3696,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3754,7 +3739,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3768,10 +3753,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45441</v>
+        <v>45567</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3784,7 +3769,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3827,7 +3812,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3841,10 +3826,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45240</v>
+        <v>46078</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3856,8 +3841,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3900,7 +3890,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3914,10 +3904,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45769</v>
+        <v>46078</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3929,8 +3919,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3973,7 +3968,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3987,10 +3982,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45782</v>
+        <v>46078</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4002,8 +3997,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4063,7 +4063,7 @@
         <v>45378</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45321</v>
+        <v>46196</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 43672-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46196</v>
+        <v>46316</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45371</v>
+        <v>46230</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.7</v>
+        <v>7.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44586</v>
+        <v>46281</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4421,14 +4421,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45084</v>
+        <v>46239</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46230</v>
+        <v>46244</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>7.6</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 41561-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46281</v>
+        <v>46301</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4640,14 +4640,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46239</v>
+        <v>45072</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4720,7 +4720,7 @@
         <v>45271</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46244</v>
+        <v>46261</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45072</v>
+        <v>45321</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 41561-2026</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46301</v>
+        <v>44586</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46261</v>
+        <v>45337</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 43672-2026</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46316</v>
+        <v>45659</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5158,7 +5158,7 @@
         <v>45737</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>46028</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>46308</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 62768-2025</t>
+          <t>A 49789-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46008</v>
+        <v>45212</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,13 +1073,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1106,160 +1106,160 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Klippfrullania
+Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 62768-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
         <v>4</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>4</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Tjäder</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 62768-2025 artfynd.xlsx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 62768-2025 karta.png", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 62768-2025 georefererad karta.tif", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 62768-2025 FSC-klagomål.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 62768-2025 FSC-klagomål mail.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 62768-2025 tillsynsbegäran.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 62768-2025 tillsynsbegäran mail.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 62768-2025 prioriterade fågelarter.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 49789-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45212</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Klippfrullania
-Trubbfjädermossa</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 46379-2025</t>
+          <t>A 48265-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1269,14 +1269,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45925</v>
+        <v>45933</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1322,267 +1322,267 @@
         <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
         <v>3</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
+          <t>Timmerticka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 23796-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Vitplätt
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 46379-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>Spillkråka
 Fiskgjuse</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 48265-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45933</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Timmerticka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 48265-2025 artfynd.xlsx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 48265-2025 karta.png", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 48265-2025 georefererad karta.tif", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 48265-2025 FSC-klagomål.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 48265-2025 FSC-klagomål mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 48265-2025 tillsynsbegäran.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 48265-2025 tillsynsbegäran mail.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 48265-2025 prioriterade fågelarter.docx", "A 48265-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 23796-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46164</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Vitplätt
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 23796-2026 artfynd.xlsx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 23796-2026 karta.png", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 23796-2026 georefererad karta.tif", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 23796-2026 FSC-klagomål.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 23796-2026 FSC-klagomål mail.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 23796-2026 tillsynsbegäran.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 23796-2026 tillsynsbegäran mail.docx", "A 23796-2026")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 23796-2026 prioriterade fågelarter.docx", "A 23796-2026")</f>
         <v/>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 2842-2025</t>
+          <t>A 44926-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45677</v>
+        <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1981,53 +1981,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 34574-2025</t>
+          <t>A 2842-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2041,10 +2037,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45847</v>
+        <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2057,7 +2053,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2090,49 +2086,53 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 6042-2024</t>
+          <t>A 34574-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45336</v>
+        <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2162,13 +2162,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>7.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2202,42 +2202,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 44926-2025</t>
+          <t>A 6042-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45918</v>
+        <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2303,39 +2303,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 6042-2024 artfynd.xlsx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 6042-2024 karta.png", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 6042-2024 georefererad karta.tif", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 6042-2024 FSC-klagomål.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 6042-2024 FSC-klagomål mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 6042-2024 tillsynsbegäran.docx", "A 6042-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 6042-2024 tillsynsbegäran mail.docx", "A 6042-2024")</f>
         <v/>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 23877-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44564</v>
+        <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2644,7 +2644,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 23877-2022</t>
+          <t>A 26650-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44722</v>
+        <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 26650-2022</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44739</v>
+        <v>45084</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44977</v>
+        <v>45734</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45734</v>
+        <v>45337</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45644</v>
+        <v>45782</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3009,7 +3009,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45127</v>
+        <v>45371</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45880</v>
+        <v>44564</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3155,7 +3155,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45371</v>
+        <v>45271</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45084</v>
+        <v>46196</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3301,7 +3301,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45240</v>
+        <v>45072</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3374,7 +3374,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45645</v>
+        <v>46230</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45782</v>
+        <v>45645</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.9</v>
+        <v>6.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3520,7 +3520,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45371</v>
+        <v>46281</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3603,14 +3603,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45769</v>
+        <v>46239</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3666,7 +3666,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45441</v>
+        <v>46244</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3739,7 +3739,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45567</v>
+        <v>46078</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3768,8 +3768,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3829,7 +3834,7 @@
         <v>46078</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3890,7 +3895,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3907,7 +3912,7 @@
         <v>46078</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3925,7 +3930,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3968,7 +3973,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 41561-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3982,10 +3987,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46078</v>
+        <v>46301</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3997,13 +4002,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45378</v>
+        <v>46261</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46196</v>
+        <v>45127</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 43672-2026</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46316</v>
+        <v>45880</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 43672-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46230</v>
+        <v>46316</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>7.6</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46281</v>
+        <v>44977</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4421,14 +4421,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46239</v>
+        <v>45644</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46244</v>
+        <v>45659</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 41561-2026</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46301</v>
+        <v>45567</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45072</v>
+        <v>45441</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45271</v>
+        <v>45240</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46261</v>
+        <v>45769</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45321</v>
+        <v>45378</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44586</v>
+        <v>45321</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45337</v>
+        <v>45371</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45659</v>
+        <v>44586</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5158,7 +5158,7 @@
         <v>45737</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>46028</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>46308</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>45212</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45933</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>45925</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>45084</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>45734</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>45337</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>45782</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>45371</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>44564</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>45271</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>46196</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>45072</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>46230</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45645</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>46281</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>46239</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>46244</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>46078</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>46078</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>46078</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>46301</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>46261</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45127</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>45880</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>46316</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>44977</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>45644</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>45659</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>45567</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>45441</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>45240</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>45769</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>45378</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45321</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45371</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>44586</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>45737</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>46028</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>46308</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>45212</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45933</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>45925</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>45084</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>45734</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>45337</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>45782</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>45371</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>44564</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>45271</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>46196</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>45072</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>46230</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45645</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>46281</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>46239</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>46244</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>46078</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>46078</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>46078</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>46301</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>46261</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45127</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>45880</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>46316</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>44977</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>45644</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>45659</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>45567</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>45441</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>45240</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>45769</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>45378</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45321</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45371</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>44586</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>45737</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>46028</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>46308</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>45212</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45933</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 46379-2025</t>
+          <t>A 46384-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1489,14 +1489,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
         <v>45925</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="J10" t="n">
         <v>2</v>
@@ -1518,7 +1518,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1533,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1542,157 +1542,157 @@
         <v>2</v>
       </c>
       <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Duvhök
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46384-2025 artfynd.xlsx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46384-2025 karta.png", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46384-2025 georefererad karta.tif", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46384-2025 FSC-klagomål.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46384-2025 FSC-klagomål mail.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46384-2025 tillsynsbegäran.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46384-2025 tillsynsbegäran mail.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46384-2025 prioriterade fågelarter.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 46379-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Fiskgjuse</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 46384-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45925</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Duvhök
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46384-2025 artfynd.xlsx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46384-2025 karta.png", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46384-2025 georefererad karta.tif", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46384-2025 FSC-klagomål.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46384-2025 FSC-klagomål mail.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46384-2025 tillsynsbegäran.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46384-2025 tillsynsbegäran mail.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46384-2025 prioriterade fågelarter.docx", "A 46384-2025")</f>
         <v/>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45084</v>
+        <v>45734</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45734</v>
+        <v>45084</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45337</v>
+        <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45782</v>
+        <v>45240</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3009,7 +3009,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3026,7 +3026,7 @@
         <v>45371</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44564</v>
+        <v>45769</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3155,7 +3155,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45271</v>
+        <v>45441</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3245,7 +3245,7 @@
         <v>46196</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45072</v>
+        <v>45567</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3374,7 +3374,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46230</v>
+        <v>45378</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>7.6</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3464,7 +3464,7 @@
         <v>45645</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46281</v>
+        <v>45127</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3603,14 +3603,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46239</v>
+        <v>45880</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3666,7 +3666,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46244</v>
+        <v>46078</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3695,8 +3695,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3756,7 +3761,7 @@
         <v>46078</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3817,7 +3822,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3834,7 +3839,7 @@
         <v>46078</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3852,7 +3857,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3895,7 +3900,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3909,10 +3914,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46078</v>
+        <v>46230</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3924,13 +3929,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 41561-2026</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46301</v>
+        <v>45072</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46261</v>
+        <v>46281</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45127</v>
+        <v>45271</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4202,14 +4202,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45880</v>
+        <v>46239</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 43672-2026</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46316</v>
+        <v>45321</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44977</v>
+        <v>44586</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45644</v>
+        <v>45337</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45659</v>
+        <v>46244</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45567</v>
+        <v>45659</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45441</v>
+        <v>44977</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45240</v>
+        <v>45782</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45769</v>
+        <v>45644</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 41561-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45378</v>
+        <v>46301</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45321</v>
+        <v>46261</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5012,7 +5012,7 @@
         <v>45371</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 43672-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44586</v>
+        <v>46316</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5158,7 +5158,7 @@
         <v>45737</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>46028</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>46308</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>45212</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45933</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 46384-2025</t>
+          <t>A 46379-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1489,14 +1489,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
         <v>45925</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
         <v>2</v>
@@ -1518,7 +1518,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1533,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1542,157 +1542,157 @@
         <v>2</v>
       </c>
       <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 46384-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Duvhök
 Tjäder</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46384-2025 artfynd.xlsx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46384-2025 karta.png", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46384-2025 georefererad karta.tif", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46384-2025 FSC-klagomål.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46384-2025 FSC-klagomål mail.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46384-2025 tillsynsbegäran.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46384-2025 tillsynsbegäran mail.docx", "A 46384-2025")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46384-2025 prioriterade fågelarter.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 46379-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45925</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Fiskgjuse</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
         <v/>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45677</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45734</v>
+        <v>45072</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45084</v>
+        <v>44977</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44564</v>
+        <v>45337</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45240</v>
+        <v>45644</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3009,7 +3009,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3026,7 +3026,7 @@
         <v>45371</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45769</v>
+        <v>44564</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3155,7 +3155,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45441</v>
+        <v>45659</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3228,7 +3228,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46196</v>
+        <v>45734</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3318,7 +3318,7 @@
         <v>45567</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45378</v>
+        <v>45441</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3464,7 +3464,7 @@
         <v>45645</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45127</v>
+        <v>45240</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45880</v>
+        <v>45769</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3666,7 +3666,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46078</v>
+        <v>46230</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3695,13 +3695,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>7.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3744,7 +3739,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3758,10 +3753,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46078</v>
+        <v>46281</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3773,13 +3768,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3822,7 +3812,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3832,14 +3822,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46078</v>
+        <v>46239</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3851,13 +3841,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3900,7 +3885,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3914,10 +3899,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46230</v>
+        <v>45378</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3930,7 +3915,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>7.6</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3973,7 +3958,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3987,10 +3972,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45072</v>
+        <v>46078</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4000,6 +3985,11 @@
       <c r="G40" t="inlineStr">
         <is>
           <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -4046,7 +4036,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4060,10 +4050,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46281</v>
+        <v>46078</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4075,8 +4065,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4119,7 +4114,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4133,10 +4128,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45271</v>
+        <v>46078</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4148,8 +4143,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4202,14 +4202,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46239</v>
+        <v>45321</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45321</v>
+        <v>46244</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44586</v>
+        <v>45371</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45337</v>
+        <v>44586</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46244</v>
+        <v>45084</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 41561-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45659</v>
+        <v>46301</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44977</v>
+        <v>46261</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 43672-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45782</v>
+        <v>46316</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45644</v>
+        <v>45271</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 41561-2026</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46301</v>
+        <v>45127</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46261</v>
+        <v>45880</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45371</v>
+        <v>45782</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 43672-2026</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46316</v>
+        <v>46196</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5158,7 +5158,7 @@
         <v>45737</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>46028</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>46308</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 49789-2023</t>
+          <t>A 62768-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45212</v>
+        <v>46008</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,13 +1073,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1106,153 +1106,153 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 62768-2025 artfynd.xlsx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 62768-2025 karta.png", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 62768-2025 georefererad karta.tif", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 62768-2025 FSC-klagomål.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 62768-2025 FSC-klagomål mail.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 62768-2025 tillsynsbegäran.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 62768-2025 tillsynsbegäran mail.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 62768-2025 prioriterade fågelarter.docx", "A 62768-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 49789-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45212</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Klippfrullania
 Trubbfjädermossa</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 62768-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46008</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>4</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 62768-2025 artfynd.xlsx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 62768-2025 karta.png", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 62768-2025 georefererad karta.tif", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 62768-2025 FSC-klagomål.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 62768-2025 FSC-klagomål mail.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 62768-2025 tillsynsbegäran.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 62768-2025 tillsynsbegäran mail.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 62768-2025 prioriterade fågelarter.docx", "A 62768-2025")</f>
         <v/>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
         <v>45933</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 46379-2025</t>
+          <t>A 46384-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1489,14 +1489,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
         <v>45925</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="J10" t="n">
         <v>2</v>
@@ -1518,7 +1518,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1533,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1542,157 +1542,157 @@
         <v>2</v>
       </c>
       <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Duvhök
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46384-2025 artfynd.xlsx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46384-2025 karta.png", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46384-2025 georefererad karta.tif", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46384-2025 FSC-klagomål.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46384-2025 FSC-klagomål mail.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46384-2025 tillsynsbegäran.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46384-2025 tillsynsbegäran mail.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46384-2025 prioriterade fågelarter.docx", "A 46384-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 46379-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Fiskgjuse</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46379-2025 artfynd.xlsx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46379-2025 karta.png", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46379-2025 georefererad karta.tif", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46379-2025 FSC-klagomål.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46379-2025 FSC-klagomål mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46379-2025 tillsynsbegäran.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46379-2025 tillsynsbegäran mail.docx", "A 46379-2025")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46379-2025 prioriterade fågelarter.docx", "A 46379-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 46384-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45925</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Duvhök
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 46384-2025 artfynd.xlsx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 46384-2025 karta.png", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 46384-2025 georefererad karta.tif", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 46384-2025 FSC-klagomål.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 46384-2025 FSC-klagomål mail.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 46384-2025 tillsynsbegäran.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 46384-2025 tillsynsbegäran mail.docx", "A 46384-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 46384-2025 prioriterade fågelarter.docx", "A 46384-2025")</f>
         <v/>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 44926-2025</t>
+          <t>A 2842-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45918</v>
+        <v>45677</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1981,49 +1981,53 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2842-2025</t>
+          <t>A 44926-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2037,10 +2041,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45677</v>
+        <v>45918</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2053,7 +2057,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2086,46 +2090,42 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 2842-2025 artfynd.xlsx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 2842-2025 karta.png", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 2842-2025 georefererad karta.tif", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 2842-2025 FSC-klagomål.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 2842-2025 FSC-klagomål mail.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 2842-2025 tillsynsbegäran.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 2842-2025 tillsynsbegäran mail.docx", "A 2842-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 2842-2025 prioriterade fågelarter.docx", "A 2842-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
         <v>45847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 26650-2022</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44739</v>
+        <v>45321</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2717,7 +2717,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45072</v>
+        <v>44586</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44977</v>
+        <v>45337</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 26650-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45337</v>
+        <v>44739</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45644</v>
+        <v>44564</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3009,7 +3009,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45371</v>
+        <v>45659</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44564</v>
+        <v>45734</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3155,7 +3155,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45659</v>
+        <v>44977</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3228,7 +3228,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45734</v>
+        <v>45127</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3301,7 +3301,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45567</v>
+        <v>45644</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3374,7 +3374,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45441</v>
+        <v>45880</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 61178-2024</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45645</v>
+        <v>45371</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3520,7 +3520,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45240</v>
+        <v>45782</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 61178-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45769</v>
+        <v>45645</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.8</v>
+        <v>6.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3666,7 +3666,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46230</v>
+        <v>45084</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>7.6</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3739,7 +3739,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 38274-2026</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46281</v>
+        <v>45240</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3812,7 +3812,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3822,14 +3822,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46239</v>
+        <v>46196</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3885,7 +3885,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45378</v>
+        <v>46078</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3914,8 +3914,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3975,7 +3980,7 @@
         <v>46078</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4036,7 +4041,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4053,7 +4058,7 @@
         <v>46078</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4071,7 +4076,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4114,7 +4119,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4128,10 +4133,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46078</v>
+        <v>45371</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4143,13 +4148,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45321</v>
+        <v>45769</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46244</v>
+        <v>45441</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45371</v>
+        <v>46230</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.7</v>
+        <v>7.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4421,14 +4421,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44586</v>
+        <v>46239</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45084</v>
+        <v>45567</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 41561-2026</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46301</v>
+        <v>45378</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46261</v>
+        <v>46244</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 43672-2026</t>
+          <t>A 41561-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46316</v>
+        <v>46301</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45271</v>
+        <v>46261</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 43672-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45127</v>
+        <v>46316</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45880</v>
+        <v>45072</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45782</v>
+        <v>45271</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 38274-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46196</v>
+        <v>46281</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5158,7 +5158,7 @@
         <v>45737</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>46028</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>46308</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>

--- a/Översikt MÖLNDAL.xlsx
+++ b/Översikt MÖLNDAL.xlsx
@@ -601,7 +601,7 @@
         <v>45833</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45645</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44551</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45663</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 62768-2025</t>
+          <t>A 49789-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46008</v>
+        <v>45212</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,13 +1073,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1106,153 +1106,153 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Klippfrullania
+Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 62768-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46326</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MÖLNDAL</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
         <v>4</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>4</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Tjäder</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 62768-2025 artfynd.xlsx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 62768-2025 karta.png", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 62768-2025 georefererad karta.tif", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 62768-2025 FSC-klagomål.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 62768-2025 FSC-klagomål mail.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 62768-2025 tillsynsbegäran.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 62768-2025 tillsynsbegäran mail.docx", "A 62768-2025")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1481/fåglar/A 62768-2025 prioriterade fågelarter.docx", "A 62768-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 49789-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45212</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46324</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Klippfrullania
-Trubbfjädermossa</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 49789-2023 artfynd.xlsx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 49789-2023 karta.png", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 49789-2023 georefererad karta.tif", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 49789-2023 FSC-klagomål.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 49789-2023 FSC-klagomål mail.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 49789-2023 tillsynsbegäran.docx", "A 49789-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 49789-2023 tillsynsbegäran mail.docx", "A 49789-2023")</f>
         <v/>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
         <v>45933</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>45925</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>44831</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44586</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45677</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 44926-2025</t>
+          <t>A 34574-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45918</v>
+        <v>45847</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.8</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2093,46 +2093,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 34574-2025</t>
+          <t>A 44926-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45847</v>
+        <v>45918</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.4</v>
+        <v>3.8</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2198,39 +2198,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 34574-2025 artfynd.xlsx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/artfynd/A 44926-2025 artfynd.xlsx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 34574-2025 karta.png", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor/A 44926-2025 karta.png", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 34574-2025 georefererad karta.tif", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/kartor_geotiff/A 44926-2025 georefererad karta.tif", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 34574-2025 FSC-klagomål.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomål/A 44926-2025 FSC-klagomål.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 34574-2025 FSC-klagomål mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/klagomålsmail/A 44926-2025 FSC-klagomål mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 34574-2025 tillsynsbegäran.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsyn/A 44926-2025 tillsynsbegäran.docx", "A 44926-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 34574-2025 tillsynsbegäran mail.docx", "A 34574-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1481/tillsynsmail/A 44926-2025 tillsynsbegäran mail.docx", "A 44926-2025")</f>
         <v/>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
         <v>45336</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44516</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44831</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>44586</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44722</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 3811-2024</t>
+          <t>A 26650-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45321</v>
+        <v>44739</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2717,7 +2717,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 3676-2022</t>
+          <t>A 38-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44586</v>
+        <v>44564</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 6258-2024</t>
+          <t>A 21536-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45337</v>
+        <v>45441</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 26650-2022</t>
+          <t>A 12977-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44739</v>
+        <v>45734</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 38-2022</t>
+          <t>A 43067-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44564</v>
+        <v>45567</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3009,7 +3009,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 88-2025</t>
+          <t>A 12273-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45659</v>
+        <v>45378</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12977-2025</t>
+          <t>A 33201-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45734</v>
+        <v>45127</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3155,7 +3155,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 8639-2023</t>
+          <t>A 37570-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44977</v>
+        <v>45880</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3228,7 +3228,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33201-2023</t>
+          <t>A 10672-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45127</v>
+        <v>46078</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3257,8 +3257,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3301,7 +3306,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 60809-2024</t>
+          <t>A 10661-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3315,10 +3320,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45644</v>
+        <v>46078</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3330,8 +3335,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3374,7 +3384,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 37570-2025</t>
+          <t>A 10654-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3388,10 +3398,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45880</v>
+        <v>46078</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3403,8 +3413,13 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3447,7 +3462,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 11256-2024</t>
+          <t>A 22953-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3461,10 +3476,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45371</v>
+        <v>45072</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3477,7 +3492,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3520,7 +3535,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 21477-2025</t>
+          <t>A 62804-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3534,10 +3549,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45782</v>
+        <v>45271</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3550,7 +3565,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3610,7 +3625,7 @@
         <v>45645</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3666,7 +3681,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 24771-2023</t>
+          <t>A 3811-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3680,10 +3695,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45084</v>
+        <v>45321</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3696,7 +3711,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3739,7 +3754,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 56133-2023</t>
+          <t>A 3676-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3753,10 +3768,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45240</v>
+        <v>44586</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3769,7 +3784,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3812,7 +3827,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28291-2026</t>
+          <t>A 6258-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3826,10 +3841,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46196</v>
+        <v>45337</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3842,7 +3857,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3885,7 +3900,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10672-2026</t>
+          <t>A 88-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3899,10 +3914,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46078</v>
+        <v>45659</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3912,11 +3927,6 @@
       <c r="G39" t="inlineStr">
         <is>
           <t>MÖLNDAL</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -3963,7 +3973,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10661-2026</t>
+          <t>A 8639-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3977,10 +3987,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46078</v>
+        <v>44977</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3992,13 +4002,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4041,7 +4046,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10654-2026</t>
+          <t>A 60809-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4055,10 +4060,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46078</v>
+        <v>45644</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4070,13 +4075,8 @@
           <t>MÖLNDAL</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 11261-2024</t>
+          <t>A 21477-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45371</v>
+        <v>45782</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 19295-2025</t>
+          <t>A 11256-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45769</v>
+        <v>45371</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 21536-2024</t>
+          <t>A 28291-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45441</v>
+        <v>46196</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 31828-2026</t>
+          <t>A 24771-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46230</v>
+        <v>45084</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>7.6</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 32581-2026</t>
+          <t>A 56133-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4421,14 +4421,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46239</v>
+        <v>45240</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 43067-2024</t>
+          <t>A 31828-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45567</v>
+        <v>46230</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 12273-2024</t>
+          <t>A 32581-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4567,14 +4567,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45378</v>
+        <v>46239</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 32941-2026</t>
+          <t>A 11261-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46244</v>
+        <v>45371</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 41561-2026</t>
+          <t>A 32941-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46301</v>
+        <v>46244</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 35293-2026</t>
+          <t>A 19295-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46261</v>
+        <v>45769</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 43672-2026</t>
+          <t>A 41561-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46316</v>
+        <v>46301</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22953-2023</t>
+          <t>A 35293-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45072</v>
+        <v>46261</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 62804-2023</t>
+          <t>A 43672-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45271</v>
+        <v>46316</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5085,7 +5085,7 @@
         <v>46281</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>45737</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>46028</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>46308</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
